--- a/artfynd/A 55492-2025 artfynd.xlsx
+++ b/artfynd/A 55492-2025 artfynd.xlsx
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129921260</v>
+        <v>129921255</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,34 +1338,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506129</v>
+        <v>505796</v>
       </c>
       <c r="R8" t="n">
-        <v>7041423</v>
+        <v>7041482</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1405,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Rikligt på en 1m hög granstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,8 +1414,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1429,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129921255</v>
+        <v>129921264</v>
       </c>
       <c r="B9" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,37 +1464,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505796</v>
+        <v>505965</v>
       </c>
       <c r="R9" t="n">
-        <v>7041482</v>
+        <v>7041473</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,7 +1528,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på en 1m hög granstubbe</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,29 +1537,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1555,7 +1555,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129921264</v>
+        <v>129921260</v>
       </c>
       <c r="B10" t="n">
         <v>79081</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505965</v>
+        <v>506129</v>
       </c>
       <c r="R10" t="n">
-        <v>7041473</v>
+        <v>7041423</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129921259</v>
+        <v>129921266</v>
       </c>
       <c r="B11" t="n">
         <v>79081</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506192</v>
+        <v>505882</v>
       </c>
       <c r="R11" t="n">
-        <v>7041434</v>
+        <v>7041492</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På välhackad död gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129921266</v>
+        <v>129921259</v>
       </c>
       <c r="B12" t="n">
         <v>79081</v>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505882</v>
+        <v>506192</v>
       </c>
       <c r="R12" t="n">
-        <v>7041492</v>
+        <v>7041434</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På välhackad död gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2602,10 +2602,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129921261</v>
+        <v>129921251</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,34 +2613,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506155</v>
+        <v>506126</v>
       </c>
       <c r="R20" t="n">
-        <v>7041475</v>
+        <v>7041425</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2677,7 +2680,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Rikligt, på sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2686,8 +2689,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>vanlig sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2704,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129921251</v>
+        <v>129921261</v>
       </c>
       <c r="B21" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,37 +2734,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506126</v>
+        <v>506155</v>
       </c>
       <c r="R21" t="n">
-        <v>7041425</v>
+        <v>7041475</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2782,7 +2798,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt, på sälg</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2791,24 +2807,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>vanlig sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea subsp. caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea subsp. caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 55492-2025 artfynd.xlsx
+++ b/artfynd/A 55492-2025 artfynd.xlsx
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129921258</v>
+        <v>129921246</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,34 +1024,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506384</v>
+        <v>505962</v>
       </c>
       <c r="R5" t="n">
-        <v>7041622</v>
+        <v>7041505</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1096,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129921257</v>
+        <v>129921258</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1150,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506139</v>
+        <v>506384</v>
       </c>
       <c r="R6" t="n">
-        <v>7041701</v>
+        <v>7041622</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129921246</v>
+        <v>129921257</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1228,42 +1236,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505962</v>
+        <v>506139</v>
       </c>
       <c r="R7" t="n">
-        <v>7041505</v>
+        <v>7041701</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129921255</v>
+        <v>129921264</v>
       </c>
       <c r="B8" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,37 +1338,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505796</v>
+        <v>505965</v>
       </c>
       <c r="R8" t="n">
-        <v>7041482</v>
+        <v>7041473</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,7 +1402,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt på en 1m hög granstubbe</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,29 +1411,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1453,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129921264</v>
+        <v>129921260</v>
       </c>
       <c r="B9" t="n">
         <v>79081</v>
@@ -1488,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505965</v>
+        <v>506129</v>
       </c>
       <c r="R9" t="n">
-        <v>7041473</v>
+        <v>7041423</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129921260</v>
+        <v>129921255</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,34 +1542,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506129</v>
+        <v>505796</v>
       </c>
       <c r="R10" t="n">
-        <v>7041423</v>
+        <v>7041482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1609,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Rikligt på en 1m hög granstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,8 +1618,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 55492-2025 artfynd.xlsx
+++ b/artfynd/A 55492-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129921253</v>
       </c>
       <c r="B2" t="n">
-        <v>80222</v>
+        <v>80225</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129921245</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>129921250</v>
       </c>
       <c r="B4" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129921246</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>129921258</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>129921257</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129921264</v>
+        <v>129921255</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>91598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,34 +1338,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505965</v>
+        <v>505796</v>
       </c>
       <c r="R8" t="n">
-        <v>7041473</v>
+        <v>7041482</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1405,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Rikligt på en 1m hög granstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,8 +1414,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1429,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129921260</v>
+        <v>129921264</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506129</v>
+        <v>505965</v>
       </c>
       <c r="R9" t="n">
-        <v>7041423</v>
+        <v>7041473</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129921255</v>
+        <v>129921260</v>
       </c>
       <c r="B10" t="n">
-        <v>91595</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,37 +1566,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505796</v>
+        <v>506129</v>
       </c>
       <c r="R10" t="n">
-        <v>7041482</v>
+        <v>7041423</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1630,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt på en 1m hög granstubbe</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,29 +1639,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1660,7 +1660,7 @@
         <v>129921266</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>129921259</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>129921254</v>
       </c>
       <c r="B13" t="n">
-        <v>80222</v>
+        <v>80225</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>129921247</v>
       </c>
       <c r="B14" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>129921269</v>
       </c>
       <c r="B15" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>129921268</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>129921252</v>
       </c>
       <c r="B17" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>129921249</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>129921248</v>
       </c>
       <c r="B19" t="n">
-        <v>80215</v>
+        <v>80218</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>129921251</v>
       </c>
       <c r="B20" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>129921261</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2025 artfynd.xlsx
+++ b/artfynd/A 55492-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129921245</v>
+        <v>129921250</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>80190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,42 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506251</v>
+        <v>506222</v>
       </c>
       <c r="R3" t="n">
-        <v>7041820</v>
+        <v>7041401</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, gamla, i gran.</t>
+          <t>På fallen, knappt levande sälg, med suraler</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129921250</v>
+        <v>129921245</v>
       </c>
       <c r="B4" t="n">
-        <v>80190</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,34 +914,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506222</v>
+        <v>506251</v>
       </c>
       <c r="R4" t="n">
-        <v>7041401</v>
+        <v>7041820</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På fallen, knappt levande sälg, med suraler</t>
+          <t>Ringhack, gamla, i gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 55492-2025 artfynd.xlsx
+++ b/artfynd/A 55492-2025 artfynd.xlsx
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129921246</v>
+        <v>129921258</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,42 +1024,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505962</v>
+        <v>506384</v>
       </c>
       <c r="R5" t="n">
-        <v>7041505</v>
+        <v>7041622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129921258</v>
+        <v>129921246</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,34 +1126,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506384</v>
+        <v>505962</v>
       </c>
       <c r="R6" t="n">
-        <v>7041622</v>
+        <v>7041505</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 55492-2025 artfynd.xlsx
+++ b/artfynd/A 55492-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129921253</v>
       </c>
       <c r="B2" t="n">
-        <v>80225</v>
+        <v>80228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129921250</v>
+        <v>129921245</v>
       </c>
       <c r="B3" t="n">
-        <v>80190</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,34 +812,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506222</v>
+        <v>506251</v>
       </c>
       <c r="R3" t="n">
-        <v>7041401</v>
+        <v>7041820</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På fallen, knappt levande sälg, med suraler</t>
+          <t>Ringhack, gamla, i gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129921245</v>
+        <v>129921250</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>80193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,42 +922,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506251</v>
+        <v>506222</v>
       </c>
       <c r="R4" t="n">
-        <v>7041820</v>
+        <v>7041401</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, gamla, i gran.</t>
+          <t>På fallen, knappt levande sälg, med suraler</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1016,7 @@
         <v>129921258</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>129921246</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>129921257</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129921255</v>
+        <v>129921264</v>
       </c>
       <c r="B8" t="n">
-        <v>91598</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,37 +1338,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505796</v>
+        <v>505965</v>
       </c>
       <c r="R8" t="n">
-        <v>7041482</v>
+        <v>7041473</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,7 +1402,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt på en 1m hög granstubbe</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,29 +1411,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1453,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129921264</v>
+        <v>129921255</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>91601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,34 +1440,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505965</v>
+        <v>505796</v>
       </c>
       <c r="R9" t="n">
-        <v>7041473</v>
+        <v>7041482</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1507,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Rikligt på en 1m hög granstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,8 +1516,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1558,7 +1558,7 @@
         <v>129921260</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>129921266</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>129921259</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>129921254</v>
       </c>
       <c r="B13" t="n">
-        <v>80225</v>
+        <v>80228</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>129921247</v>
       </c>
       <c r="B14" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>129921269</v>
       </c>
       <c r="B15" t="n">
-        <v>82921</v>
+        <v>82924</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>129921268</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>129921252</v>
       </c>
       <c r="B17" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>129921249</v>
       </c>
       <c r="B18" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>129921248</v>
       </c>
       <c r="B19" t="n">
-        <v>80218</v>
+        <v>80221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>129921251</v>
       </c>
       <c r="B20" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>129921261</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2822,6 +2822,8285 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130011057</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>506098</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7041446</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt med bålar och med apothecier.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130011026</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>506225</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7041468</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i en levande stående gran.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130011943</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>506047</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7041498</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130011947</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>505728</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7041430</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130011936</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91569</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>506219</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7041490</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130011960</v>
+      </c>
+      <c r="B27" t="n">
+        <v>82924</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>505875</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7041542</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130011022</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>506105</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7041429</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130011941</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>506370</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7041567</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130011051</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>506173</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7041436</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På flera granar i granskog.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130011069</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>505714</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7041397</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130011959</v>
+      </c>
+      <c r="B32" t="n">
+        <v>82924</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>505869</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7041576</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130011027</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>505811</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7041517</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rejäla äldre hackspår i en granhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130011955</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>506094</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7041562</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130011058</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>506127</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7041473</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130011948</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>505728</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7041439</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130011036</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57844</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>505812</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7041524</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2 nyfikna lavskrikor med lockläte i flerskiktad granskog med bitvis rikligt med garnlav på gran.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130011072</v>
+      </c>
+      <c r="B38" t="n">
+        <v>89004</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>510</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>506145</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7041721</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130011944</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>506053</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7041506</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130011939</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92323</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>506013</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7041655</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130011049</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>506235</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7041415</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130011044</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>506151</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7041726</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130011060</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>505941</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7041526</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130011064</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>505859</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7041479</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130011045</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>506325</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7041726</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130011040</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91625</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>506158</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7041729</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Växer i en tvåstammig gran.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130011038</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98701</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>506139</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7041442</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 vinterståndare i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130011062</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>505881</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7041488</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130011056</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>506125</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7041395</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130011949</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>506072</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7041512</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska födosöksspår/hackspår.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130011035</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>506220</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7041401</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130011063</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>505931</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7041478</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>130011958</v>
+      </c>
+      <c r="B53" t="n">
+        <v>82924</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>506132</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7041590</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130011028</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80193</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>506225</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7041457</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På en smal rönn.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130011052</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>506151</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7041457</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>130011025</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>506100</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7041452</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Minst 2 talltitor med lockläte I äldre luckig granskog.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>130011029</v>
+      </c>
+      <c r="B57" t="n">
+        <v>97668</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>506106</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7041408</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt i granskog.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>130011054</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>506132</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7041423</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>130011053</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>506141</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7041449</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>130011068</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>505745</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7041395</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>130011033</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80192</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>506221</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7041401</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>130011937</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>506419</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7041521</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>130011935</v>
+      </c>
+      <c r="B63" t="n">
+        <v>83058</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>505879</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7041583</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>130011034</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80192</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>505800</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7041450</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>130011938</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>506088</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7041532</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>130011954</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>506077</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7041514</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Riklig förekomst med gott om garnlavsbålar.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>130011041</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91625</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>506282</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7041798</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående gran med 33 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>130011021</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>506131</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7041380</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>130011020</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>506133</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7041369</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>130011050</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>506188</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7041400</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På bark och gren av björk i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Betula</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>130011046</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>506348</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7041704</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>130011048</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>506213</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7041439</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>130011018</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>506297</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7041772</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs minst 5 meter på en granstam.</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>130011957</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>505654</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7041396</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>130011055</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>506137</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7041384</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>130011070</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>505697</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7041399</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>130011019</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>506192</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7041460</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs minst 5 meter på en granstam.</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>130011043</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>506144</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7041702</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>130011039</v>
+      </c>
+      <c r="B79" t="n">
+        <v>91601</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>506185</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7041427</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>130011942</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>506378</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7041569</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>130011023</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>505929</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7041514</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>130011065</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>505816</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7041475</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>130011956</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>505707</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7041435</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>130011024</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>505908</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7041477</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs flera meter på en gran i gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>130011059</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>506131</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7041516</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>130011953</v>
+      </c>
+      <c r="B86" t="n">
+        <v>91625</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>506196</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7041474</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>130011042</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91625</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>505757</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7041406</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>I en klen granhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>130011061</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>505949</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7041499</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>130011946</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>506026</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7041657</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>130011945</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>506106</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7041570</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>130011032</v>
+      </c>
+      <c r="B91" t="n">
+        <v>80192</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>506224</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7041455</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På en smal rönn.</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>130011066</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Kiltermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>505790</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7041427</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55492-2025 artfynd.xlsx
+++ b/artfynd/A 55492-2025 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129921246</v>
+        <v>129921257</v>
       </c>
       <c r="B6" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,42 +1126,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505962</v>
+        <v>506139</v>
       </c>
       <c r="R6" t="n">
-        <v>7041505</v>
+        <v>7041701</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1190,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129921257</v>
+        <v>129921246</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,34 +1228,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506139</v>
+        <v>505962</v>
       </c>
       <c r="R7" t="n">
-        <v>7041701</v>
+        <v>7041505</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 55492-2025 artfynd.xlsx
+++ b/artfynd/A 55492-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129921250</v>
+        <v>129921245</v>
       </c>
       <c r="B3" t="n">
-        <v>80194</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,34 +812,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506222</v>
+        <v>506251</v>
       </c>
       <c r="R3" t="n">
-        <v>7041401</v>
+        <v>7041820</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På fallen, knappt levande sälg, med suraler</t>
+          <t>Ringhack, gamla, i gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129921245</v>
+        <v>129921250</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,42 +922,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506251</v>
+        <v>506222</v>
       </c>
       <c r="R4" t="n">
-        <v>7041820</v>
+        <v>7041401</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, gamla, i gran.</t>
+          <t>På fallen, knappt levande sälg, med suraler</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2825,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130011057</v>
+        <v>130011026</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,28 +2836,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2867,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506098</v>
+        <v>506225</v>
       </c>
       <c r="R22" t="n">
-        <v>7041446</v>
+        <v>7041468</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2908,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt med bålar och med apothecier.</t>
+          <t>Äldre rejäla hackspår i en levande stående gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2916,7 +2917,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130011026</v>
+        <v>130011057</v>
       </c>
       <c r="B23" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2971,29 +2971,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3003,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506225</v>
+        <v>506098</v>
       </c>
       <c r="R23" t="n">
-        <v>7041468</v>
+        <v>7041446</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,7 +3042,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre rejäla hackspår i en levande stående gran.</t>
+          <t>Rikligt med bålar och med apothecier.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,6 +3051,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3072,12 +3072,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130011051</v>
+        <v>130011959</v>
       </c>
       <c r="B30" t="n">
-        <v>79088</v>
+        <v>82925</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3814,21 +3814,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506173</v>
+        <v>505869</v>
       </c>
       <c r="R30" t="n">
-        <v>7041436</v>
+        <v>7041576</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3876,19 +3876,35 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På flera granar i granskog.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3905,10 +3921,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130011959</v>
+        <v>130011027</v>
       </c>
       <c r="B31" t="n">
-        <v>82925</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3916,34 +3932,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505869</v>
+        <v>505811</v>
       </c>
       <c r="R31" t="n">
-        <v>7041576</v>
+        <v>7041517</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3978,13 +4002,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rejäla äldre hackspår i en granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4003,9 +4031,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4023,10 +4056,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130011027</v>
+        <v>130011051</v>
       </c>
       <c r="B32" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4034,42 +4067,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505811</v>
+        <v>506173</v>
       </c>
       <c r="R32" t="n">
-        <v>7041517</v>
+        <v>7041436</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4106,7 +4131,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i en granhögstubbe.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4117,31 +4142,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4739,10 +4739,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130011944</v>
+        <v>130011044</v>
       </c>
       <c r="B38" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4750,42 +4750,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506053</v>
+        <v>506151</v>
       </c>
       <c r="R38" t="n">
-        <v>7041506</v>
+        <v>7041726</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4822,7 +4814,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4833,11 +4825,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4956,7 +4943,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130011044</v>
+        <v>130011060</v>
       </c>
       <c r="B40" t="n">
         <v>79088</v>
@@ -4991,10 +4978,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506151</v>
+        <v>505941</v>
       </c>
       <c r="R40" t="n">
-        <v>7041726</v>
+        <v>7041526</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5058,7 +5045,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130011060</v>
+        <v>130011064</v>
       </c>
       <c r="B41" t="n">
         <v>79088</v>
@@ -5093,10 +5080,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>505941</v>
+        <v>505859</v>
       </c>
       <c r="R41" t="n">
-        <v>7041526</v>
+        <v>7041479</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5160,45 +5147,52 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130011064</v>
+        <v>130011939</v>
       </c>
       <c r="B42" t="n">
-        <v>79088</v>
+        <v>92324</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>505859</v>
+        <v>506013</v>
       </c>
       <c r="R42" t="n">
-        <v>7041479</v>
+        <v>7041655</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5233,19 +5227,35 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5262,39 +5272,40 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130011939</v>
+        <v>130011944</v>
       </c>
       <c r="B43" t="n">
-        <v>92324</v>
+        <v>57740</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5304,10 +5315,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506013</v>
+        <v>506053</v>
       </c>
       <c r="R43" t="n">
-        <v>7041655</v>
+        <v>7041506</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5342,34 +5353,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5502,53 +5502,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130011038</v>
+        <v>130011045</v>
       </c>
       <c r="B45" t="n">
-        <v>98702</v>
+        <v>79088</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506139</v>
+        <v>506325</v>
       </c>
       <c r="R45" t="n">
-        <v>7041442</v>
+        <v>7041726</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5585,7 +5577,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>1 vinterståndare i äldre granskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5594,14 +5586,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5618,7 +5604,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130011045</v>
+        <v>130011062</v>
       </c>
       <c r="B46" t="n">
         <v>79088</v>
@@ -5653,10 +5639,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506325</v>
+        <v>505881</v>
       </c>
       <c r="R46" t="n">
-        <v>7041726</v>
+        <v>7041488</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5693,7 +5679,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5720,7 +5706,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130011062</v>
+        <v>130011056</v>
       </c>
       <c r="B47" t="n">
         <v>79088</v>
@@ -5755,10 +5741,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505881</v>
+        <v>506125</v>
       </c>
       <c r="R47" t="n">
-        <v>7041488</v>
+        <v>7041395</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5795,7 +5781,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5822,10 +5808,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130011056</v>
+        <v>130011040</v>
       </c>
       <c r="B48" t="n">
-        <v>79088</v>
+        <v>91626</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5833,34 +5819,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506125</v>
+        <v>506158</v>
       </c>
       <c r="R48" t="n">
-        <v>7041395</v>
+        <v>7041729</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5897,7 +5886,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Växer i en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5906,8 +5895,34 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5924,37 +5939,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130011040</v>
+        <v>130011038</v>
       </c>
       <c r="B49" t="n">
-        <v>91626</v>
+        <v>98702</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>220093</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5962,10 +5982,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506158</v>
+        <v>506139</v>
       </c>
       <c r="R49" t="n">
-        <v>7041729</v>
+        <v>7041442</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6002,7 +6022,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Växer i en tvåstammig gran.</t>
+          <t>1 vinterståndare i äldre granskog.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6018,26 +6038,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7561,10 +7561,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130011954</v>
+        <v>130011938</v>
       </c>
       <c r="B63" t="n">
-        <v>79088</v>
+        <v>91606</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7572,26 +7572,30 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7599,10 +7603,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506077</v>
+        <v>506088</v>
       </c>
       <c r="R63" t="n">
-        <v>7041514</v>
+        <v>7041532</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7637,11 +7641,6 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Riklig förekomst med gott om garnlavsbålar.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7655,6 +7654,21 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7672,10 +7686,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130011938</v>
+        <v>130011954</v>
       </c>
       <c r="B64" t="n">
-        <v>91606</v>
+        <v>79088</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7683,30 +7697,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7714,10 +7724,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506088</v>
+        <v>506077</v>
       </c>
       <c r="R64" t="n">
-        <v>7041532</v>
+        <v>7041514</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7752,6 +7762,11 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Riklig förekomst med gott om garnlavsbålar.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7765,21 +7780,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8562,10 +8562,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130011018</v>
+        <v>130011048</v>
       </c>
       <c r="B71" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8573,42 +8573,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506297</v>
+        <v>506213</v>
       </c>
       <c r="R71" t="n">
-        <v>7041772</v>
+        <v>7041439</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8645,7 +8637,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 5 meter på en granstam.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8656,31 +8648,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8697,7 +8664,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130011048</v>
+        <v>130011957</v>
       </c>
       <c r="B72" t="n">
         <v>79088</v>
@@ -8726,16 +8693,19 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506213</v>
+        <v>505654</v>
       </c>
       <c r="R72" t="n">
-        <v>7041439</v>
+        <v>7041396</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8770,19 +8740,20 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8799,10 +8770,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130011957</v>
+        <v>130011018</v>
       </c>
       <c r="B73" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8810,26 +8781,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8837,10 +8813,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>505654</v>
+        <v>506297</v>
       </c>
       <c r="R73" t="n">
-        <v>7041396</v>
+        <v>7041772</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8875,19 +8851,43 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs minst 5 meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9731,10 +9731,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130011065</v>
+        <v>130011024</v>
       </c>
       <c r="B81" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9742,34 +9742,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505816</v>
+        <v>505908</v>
       </c>
       <c r="R81" t="n">
-        <v>7041475</v>
+        <v>7041477</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9806,7 +9814,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9817,6 +9825,31 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9833,7 +9866,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130011956</v>
+        <v>130011065</v>
       </c>
       <c r="B82" t="n">
         <v>79088</v>
@@ -9862,19 +9895,16 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505707</v>
+        <v>505816</v>
       </c>
       <c r="R82" t="n">
-        <v>7041435</v>
+        <v>7041475</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9911,7 +9941,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9920,14 +9950,8 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9944,7 +9968,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130011059</v>
+        <v>130011956</v>
       </c>
       <c r="B83" t="n">
         <v>79088</v>
@@ -9973,16 +9997,19 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506131</v>
+        <v>505707</v>
       </c>
       <c r="R83" t="n">
-        <v>7041516</v>
+        <v>7041435</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10019,7 +10046,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10028,8 +10055,14 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10046,10 +10079,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130011953</v>
+        <v>130011059</v>
       </c>
       <c r="B84" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10057,37 +10090,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506196</v>
+        <v>506131</v>
       </c>
       <c r="R84" t="n">
-        <v>7041474</v>
+        <v>7041516</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10122,35 +10152,19 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10167,7 +10181,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130011042</v>
+        <v>130011953</v>
       </c>
       <c r="B85" t="n">
         <v>91626</v>
@@ -10205,10 +10219,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>505757</v>
+        <v>506196</v>
       </c>
       <c r="R85" t="n">
-        <v>7041406</v>
+        <v>7041474</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10243,11 +10257,6 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>I en klen granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10273,14 +10282,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10298,10 +10302,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130011024</v>
+        <v>130011042</v>
       </c>
       <c r="B86" t="n">
-        <v>57740</v>
+        <v>91626</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10309,29 +10313,24 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -10341,10 +10340,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>505908</v>
+        <v>505757</v>
       </c>
       <c r="R86" t="n">
-        <v>7041477</v>
+        <v>7041406</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10381,7 +10380,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran i gammal granskog.</t>
+          <t>I en klen granhögstubbe.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10390,6 +10389,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10410,12 +10410,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10650,10 +10650,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130011945</v>
+        <v>130011032</v>
       </c>
       <c r="B89" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10661,29 +10661,28 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -10693,10 +10692,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>506106</v>
+        <v>506224</v>
       </c>
       <c r="R89" t="n">
-        <v>7041570</v>
+        <v>7041455</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10733,7 +10732,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På en smal rönn.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10742,12 +10741,33 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10867,10 +10887,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130011032</v>
+        <v>130011945</v>
       </c>
       <c r="B91" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10878,28 +10898,29 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -10909,10 +10930,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>506224</v>
+        <v>506106</v>
       </c>
       <c r="R91" t="n">
-        <v>7041455</v>
+        <v>7041570</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10949,7 +10970,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På en smal rönn.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10958,33 +10979,12 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -13096,10 +13096,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130022278</v>
+        <v>130022268</v>
       </c>
       <c r="B110" t="n">
-        <v>91606</v>
+        <v>83059</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13107,30 +13107,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -13138,10 +13134,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506225</v>
+        <v>506167</v>
       </c>
       <c r="R110" t="n">
-        <v>7041439</v>
+        <v>7041474</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13201,14 +13197,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -13226,10 +13217,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130022268</v>
+        <v>130022278</v>
       </c>
       <c r="B111" t="n">
-        <v>83059</v>
+        <v>91606</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13237,26 +13228,30 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -13264,10 +13259,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>506167</v>
+        <v>506225</v>
       </c>
       <c r="R111" t="n">
-        <v>7041474</v>
+        <v>7041439</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13327,9 +13322,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -13347,7 +13347,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130022288</v>
+        <v>130022310</v>
       </c>
       <c r="B112" t="n">
         <v>57740</v>
@@ -13380,7 +13380,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -13390,10 +13390,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>506328</v>
+        <v>505802</v>
       </c>
       <c r="R112" t="n">
-        <v>7041753</v>
+        <v>7041546</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13462,7 +13462,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130022310</v>
+        <v>130022284</v>
       </c>
       <c r="B113" t="n">
         <v>57740</v>
@@ -13505,10 +13505,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>505802</v>
+        <v>506133</v>
       </c>
       <c r="R113" t="n">
-        <v>7041546</v>
+        <v>7041711</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13692,7 +13692,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130022284</v>
+        <v>130022298</v>
       </c>
       <c r="B115" t="n">
         <v>57740</v>
@@ -13735,10 +13735,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>506133</v>
+        <v>506051</v>
       </c>
       <c r="R115" t="n">
-        <v>7041711</v>
+        <v>7041538</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13807,10 +13807,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130022298</v>
+        <v>130022279</v>
       </c>
       <c r="B116" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13818,29 +13818,28 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -13850,10 +13849,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>506051</v>
+        <v>505790</v>
       </c>
       <c r="R116" t="n">
-        <v>7041538</v>
+        <v>7041489</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13888,23 +13887,39 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13922,10 +13937,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130022279</v>
+        <v>130022335</v>
       </c>
       <c r="B117" t="n">
-        <v>91606</v>
+        <v>91602</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13933,21 +13948,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13964,10 +13979,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>505790</v>
+        <v>506111</v>
       </c>
       <c r="R117" t="n">
-        <v>7041489</v>
+        <v>7041602</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14027,14 +14042,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14052,10 +14062,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130022335</v>
+        <v>130022322</v>
       </c>
       <c r="B118" t="n">
-        <v>91602</v>
+        <v>91557</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14063,21 +14073,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>112</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14094,10 +14104,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>506111</v>
+        <v>506082</v>
       </c>
       <c r="R118" t="n">
-        <v>7041602</v>
+        <v>7041551</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14177,10 +14187,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130022322</v>
+        <v>130022340</v>
       </c>
       <c r="B119" t="n">
-        <v>91557</v>
+        <v>91626</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14188,23 +14198,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Pat.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
@@ -14219,10 +14225,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>506082</v>
+        <v>506102</v>
       </c>
       <c r="R119" t="n">
-        <v>7041551</v>
+        <v>7041588</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14302,10 +14308,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130022340</v>
+        <v>130022314</v>
       </c>
       <c r="B120" t="n">
-        <v>91626</v>
+        <v>57740</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14313,37 +14319,54 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>506102</v>
+        <v>505807</v>
       </c>
       <c r="R120" t="n">
-        <v>7041588</v>
+        <v>7041547</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14378,34 +14401,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Födosökande hane i en yta med mycket höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved främst av gran.</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14423,7 +14435,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130022314</v>
+        <v>130022305</v>
       </c>
       <c r="B121" t="n">
         <v>57740</v>
@@ -14451,37 +14463,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>505807</v>
+        <v>505839</v>
       </c>
       <c r="R121" t="n">
-        <v>7041547</v>
+        <v>7041578</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14518,7 +14518,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Födosökande hane i en yta med mycket höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved främst av gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14550,7 +14550,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130022305</v>
+        <v>130022301</v>
       </c>
       <c r="B122" t="n">
         <v>57740</v>
@@ -14593,10 +14593,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>505839</v>
+        <v>506003</v>
       </c>
       <c r="R122" t="n">
-        <v>7041578</v>
+        <v>7041648</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14665,7 +14665,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130022301</v>
+        <v>130022308</v>
       </c>
       <c r="B123" t="n">
         <v>57740</v>
@@ -14708,10 +14708,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>506003</v>
+        <v>505820</v>
       </c>
       <c r="R123" t="n">
-        <v>7041648</v>
+        <v>7041561</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14780,10 +14780,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130022308</v>
+        <v>130022330</v>
       </c>
       <c r="B124" t="n">
-        <v>57740</v>
+        <v>78100</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14791,31 +14791,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -14823,10 +14818,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>505820</v>
+        <v>505898</v>
       </c>
       <c r="R124" t="n">
-        <v>7041561</v>
+        <v>7041518</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14861,23 +14856,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14895,10 +14901,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130022330</v>
+        <v>130022333</v>
       </c>
       <c r="B125" t="n">
-        <v>78100</v>
+        <v>91602</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14906,26 +14912,30 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -14933,10 +14943,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>505898</v>
+        <v>506291</v>
       </c>
       <c r="R125" t="n">
-        <v>7041518</v>
+        <v>7041817</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15016,7 +15026,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130022333</v>
+        <v>130022336</v>
       </c>
       <c r="B126" t="n">
         <v>91602</v>
@@ -15058,10 +15068,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>506291</v>
+        <v>505807</v>
       </c>
       <c r="R126" t="n">
-        <v>7041817</v>
+        <v>7041535</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15141,10 +15151,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130022336</v>
+        <v>130022349</v>
       </c>
       <c r="B127" t="n">
-        <v>91602</v>
+        <v>83051</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15152,30 +15162,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -15183,10 +15189,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>505807</v>
+        <v>505803</v>
       </c>
       <c r="R127" t="n">
-        <v>7041535</v>
+        <v>7041538</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15234,21 +15240,6 @@
       <c r="AH127" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -15266,10 +15257,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130022349</v>
+        <v>130022265</v>
       </c>
       <c r="B128" t="n">
-        <v>83051</v>
+        <v>83059</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15277,21 +15268,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15304,10 +15295,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>505803</v>
+        <v>506287</v>
       </c>
       <c r="R128" t="n">
-        <v>7041538</v>
+        <v>7041437</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15355,6 +15346,21 @@
       <c r="AH128" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -15372,7 +15378,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130022265</v>
+        <v>130022267</v>
       </c>
       <c r="B129" t="n">
         <v>83059</v>
@@ -15410,10 +15416,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>506287</v>
+        <v>506213</v>
       </c>
       <c r="R129" t="n">
-        <v>7041437</v>
+        <v>7041527</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15493,7 +15499,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130022267</v>
+        <v>130022272</v>
       </c>
       <c r="B130" t="n">
         <v>83059</v>
@@ -15531,10 +15537,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>506213</v>
+        <v>505861</v>
       </c>
       <c r="R130" t="n">
-        <v>7041527</v>
+        <v>7041553</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15614,10 +15620,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130022272</v>
+        <v>130022300</v>
       </c>
       <c r="B131" t="n">
-        <v>83059</v>
+        <v>57740</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15625,26 +15631,31 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
@@ -15652,10 +15663,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>505861</v>
+        <v>506005</v>
       </c>
       <c r="R131" t="n">
-        <v>7041553</v>
+        <v>7041651</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15690,34 +15701,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15735,7 +15735,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130022300</v>
+        <v>130022306</v>
       </c>
       <c r="B132" t="n">
         <v>57740</v>
@@ -15768,7 +15768,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>506005</v>
+        <v>505833</v>
       </c>
       <c r="R132" t="n">
-        <v>7041651</v>
+        <v>7041571</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15850,10 +15850,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130022306</v>
+        <v>130022280</v>
       </c>
       <c r="B133" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15861,29 +15861,28 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -15893,10 +15892,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>505833</v>
+        <v>505798</v>
       </c>
       <c r="R133" t="n">
-        <v>7041571</v>
+        <v>7041503</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15931,23 +15930,39 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -15965,10 +15980,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130022280</v>
+        <v>130022317</v>
       </c>
       <c r="B134" t="n">
-        <v>91606</v>
+        <v>57898</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15976,41 +15991,50 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>505798</v>
+        <v>505940</v>
       </c>
       <c r="R134" t="n">
-        <v>7041503</v>
+        <v>7041639</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16051,7 +16075,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -16060,24 +16083,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>Flerskiktad skog i många delar.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -16095,61 +16103,52 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130022317</v>
+        <v>130022282</v>
       </c>
       <c r="B135" t="n">
-        <v>57898</v>
+        <v>92324</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>505940</v>
+        <v>505786</v>
       </c>
       <c r="R135" t="n">
-        <v>7041639</v>
+        <v>7041510</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16190,17 +16189,13 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>Flerskiktad skog i många delar.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -16218,39 +16213,40 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130022282</v>
+        <v>130022293</v>
       </c>
       <c r="B136" t="n">
-        <v>92324</v>
+        <v>57740</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -16260,10 +16256,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>505786</v>
+        <v>506204</v>
       </c>
       <c r="R136" t="n">
-        <v>7041510</v>
+        <v>7041525</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16298,13 +16294,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -16328,7 +16328,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130022293</v>
+        <v>130022283</v>
       </c>
       <c r="B137" t="n">
         <v>57740</v>
@@ -16371,10 +16371,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>506204</v>
+        <v>506152</v>
       </c>
       <c r="R137" t="n">
-        <v>7041525</v>
+        <v>7041714</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16443,10 +16443,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130022283</v>
+        <v>130022347</v>
       </c>
       <c r="B138" t="n">
-        <v>57740</v>
+        <v>82925</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16454,42 +16454,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>506152</v>
+        <v>505809</v>
       </c>
       <c r="R138" t="n">
-        <v>7041714</v>
+        <v>7041517</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16524,11 +16516,6 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -16537,11 +16524,6 @@
       </c>
       <c r="AG138" t="b">
         <v>0</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
@@ -16558,10 +16540,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130022347</v>
+        <v>130022316</v>
       </c>
       <c r="B139" t="n">
-        <v>82925</v>
+        <v>57898</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16569,34 +16551,50 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>505809</v>
+        <v>506108</v>
       </c>
       <c r="R139" t="n">
-        <v>7041517</v>
+        <v>7041591</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16639,6 +16637,11 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
@@ -16655,10 +16658,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130022316</v>
+        <v>130022302</v>
       </c>
       <c r="B140" t="n">
-        <v>57898</v>
+        <v>57740</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16666,50 +16669,42 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>506108</v>
+        <v>506031</v>
       </c>
       <c r="R140" t="n">
-        <v>7041591</v>
+        <v>7041663</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16742,6 +16737,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16999,10 +16999,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130022302</v>
+        <v>130022277</v>
       </c>
       <c r="B143" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17010,29 +17010,28 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -17042,10 +17041,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>506031</v>
+        <v>506376</v>
       </c>
       <c r="R143" t="n">
-        <v>7041663</v>
+        <v>7041606</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17080,23 +17079,39 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
@@ -17249,10 +17264,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130022277</v>
+        <v>130022292</v>
       </c>
       <c r="B145" t="n">
-        <v>91606</v>
+        <v>57740</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17260,28 +17275,29 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -17291,10 +17307,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>506376</v>
+        <v>506242</v>
       </c>
       <c r="R145" t="n">
-        <v>7041606</v>
+        <v>7041507</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17329,39 +17345,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -17379,7 +17379,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130022292</v>
+        <v>130022299</v>
       </c>
       <c r="B146" t="n">
         <v>57740</v>
@@ -17422,10 +17422,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>506242</v>
+        <v>506050</v>
       </c>
       <c r="R146" t="n">
-        <v>7041507</v>
+        <v>7041531</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17494,7 +17494,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130022299</v>
+        <v>130022286</v>
       </c>
       <c r="B147" t="n">
         <v>57740</v>
@@ -17537,10 +17537,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>506050</v>
+        <v>506315</v>
       </c>
       <c r="R147" t="n">
-        <v>7041531</v>
+        <v>7041762</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17609,10 +17609,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130022286</v>
+        <v>130022348</v>
       </c>
       <c r="B148" t="n">
-        <v>57740</v>
+        <v>83051</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17620,31 +17620,26 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
@@ -17652,10 +17647,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>506315</v>
+        <v>505781</v>
       </c>
       <c r="R148" t="n">
-        <v>7041762</v>
+        <v>7041499</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17690,17 +17685,13 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -17724,10 +17715,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130022332</v>
+        <v>130022341</v>
       </c>
       <c r="B149" t="n">
-        <v>56921</v>
+        <v>91626</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17735,50 +17726,37 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>505757</v>
+        <v>505857</v>
       </c>
       <c r="R149" t="n">
-        <v>7041488</v>
+        <v>7041565</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17819,12 +17797,28 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -17842,10 +17836,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130022348</v>
+        <v>130022332</v>
       </c>
       <c r="B150" t="n">
-        <v>83051</v>
+        <v>56921</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17853,37 +17847,50 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>308</v>
+        <v>102612</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>505781</v>
+        <v>505757</v>
       </c>
       <c r="R150" t="n">
-        <v>7041499</v>
+        <v>7041488</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17924,7 +17931,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -17948,10 +17954,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130022341</v>
+        <v>130022344</v>
       </c>
       <c r="B151" t="n">
-        <v>91626</v>
+        <v>82925</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17959,26 +17965,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -17986,10 +17992,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>505857</v>
+        <v>506043</v>
       </c>
       <c r="R151" t="n">
-        <v>7041565</v>
+        <v>7041532</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18069,10 +18075,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130022344</v>
+        <v>130022337</v>
       </c>
       <c r="B152" t="n">
-        <v>82925</v>
+        <v>91620</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18080,26 +18086,30 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -18107,10 +18117,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>506043</v>
+        <v>505832</v>
       </c>
       <c r="R152" t="n">
-        <v>7041532</v>
+        <v>7041497</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18158,21 +18168,6 @@
       <c r="AH152" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -18190,10 +18185,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130022337</v>
+        <v>130022346</v>
       </c>
       <c r="B153" t="n">
-        <v>91620</v>
+        <v>82925</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18201,30 +18196,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
@@ -18232,10 +18223,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>505832</v>
+        <v>505969</v>
       </c>
       <c r="R153" t="n">
-        <v>7041497</v>
+        <v>7041653</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18283,6 +18274,21 @@
       <c r="AH153" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -18300,10 +18306,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130022346</v>
+        <v>130022269</v>
       </c>
       <c r="B154" t="n">
-        <v>82925</v>
+        <v>83059</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18311,21 +18317,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18338,10 +18344,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>505969</v>
+        <v>506062</v>
       </c>
       <c r="R154" t="n">
-        <v>7041653</v>
+        <v>7041545</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18421,10 +18427,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130022270</v>
+        <v>130022296</v>
       </c>
       <c r="B155" t="n">
-        <v>83059</v>
+        <v>57740</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18432,26 +18438,31 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -18459,10 +18470,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>505972</v>
+        <v>506041</v>
       </c>
       <c r="R155" t="n">
-        <v>7041657</v>
+        <v>7041525</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18497,34 +18508,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>
@@ -18542,10 +18542,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130022318</v>
+        <v>130022313</v>
       </c>
       <c r="B156" t="n">
-        <v>57898</v>
+        <v>57740</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18553,50 +18553,42 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>505748</v>
+        <v>505812</v>
       </c>
       <c r="R156" t="n">
-        <v>7041442</v>
+        <v>7041551</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18629,6 +18621,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18660,10 +18657,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130022269</v>
+        <v>130022297</v>
       </c>
       <c r="B157" t="n">
-        <v>83059</v>
+        <v>57740</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18671,26 +18668,31 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -18701,7 +18703,7 @@
         <v>506062</v>
       </c>
       <c r="R157" t="n">
-        <v>7041545</v>
+        <v>7041558</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18736,34 +18738,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -18781,10 +18772,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130022296</v>
+        <v>130022318</v>
       </c>
       <c r="B158" t="n">
-        <v>57740</v>
+        <v>57898</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18792,42 +18783,50 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>506041</v>
+        <v>505748</v>
       </c>
       <c r="R158" t="n">
-        <v>7041525</v>
+        <v>7041442</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18860,11 +18859,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18896,10 +18890,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130022313</v>
+        <v>130022270</v>
       </c>
       <c r="B159" t="n">
-        <v>57740</v>
+        <v>83059</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18907,31 +18901,26 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -18939,10 +18928,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>505812</v>
+        <v>505972</v>
       </c>
       <c r="R159" t="n">
-        <v>7041551</v>
+        <v>7041657</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18977,23 +18966,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>
@@ -19011,42 +19011,37 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130022297</v>
+        <v>130022324</v>
       </c>
       <c r="B160" t="n">
-        <v>57740</v>
+        <v>83057</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
@@ -19054,10 +19049,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>506062</v>
+        <v>505884</v>
       </c>
       <c r="R160" t="n">
-        <v>7041558</v>
+        <v>7041508</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19092,23 +19087,39 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -19126,10 +19137,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130022324</v>
+        <v>130022319</v>
       </c>
       <c r="B161" t="n">
-        <v>83057</v>
+        <v>58375</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19137,37 +19148,50 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6486</v>
+        <v>102125</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>505884</v>
+        <v>505775</v>
       </c>
       <c r="R161" t="n">
-        <v>7041508</v>
+        <v>7041440</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19202,39 +19226,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Observerades i gammal grandominerad skog med inslag av björk och enstaka sälg och rönn.</t>
+        </is>
+      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr"/>
@@ -19252,61 +19260,52 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>130022319</v>
+        <v>130022281</v>
       </c>
       <c r="B162" t="n">
-        <v>58375</v>
+        <v>92324</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>102125</v>
+        <v>3298</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>505775</v>
+        <v>506113</v>
       </c>
       <c r="R162" t="n">
-        <v>7041440</v>
+        <v>7041592</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19341,17 +19340,13 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Observerades i gammal grandominerad skog med inslag av björk och enstaka sälg och rönn.</t>
-        </is>
-      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -19375,39 +19370,40 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>130022281</v>
+        <v>130022312</v>
       </c>
       <c r="B163" t="n">
-        <v>92324</v>
+        <v>57740</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -19417,10 +19413,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>506113</v>
+        <v>505809</v>
       </c>
       <c r="R163" t="n">
-        <v>7041592</v>
+        <v>7041553</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19455,13 +19451,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -19485,7 +19485,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130022312</v>
+        <v>130022315</v>
       </c>
       <c r="B164" t="n">
         <v>57740</v>
@@ -19518,7 +19518,7 @@
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -19528,10 +19528,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>505809</v>
+        <v>505763</v>
       </c>
       <c r="R164" t="n">
-        <v>7041553</v>
+        <v>7041524</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19568,7 +19568,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19583,6 +19583,21 @@
       <c r="AH164" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -19600,10 +19615,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130022315</v>
+        <v>130022275</v>
       </c>
       <c r="B165" t="n">
-        <v>57740</v>
+        <v>83059</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19611,31 +19626,26 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
@@ -19643,10 +19653,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>505763</v>
+        <v>505826</v>
       </c>
       <c r="R165" t="n">
-        <v>7041524</v>
+        <v>7041551</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19681,17 +19691,13 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -19730,61 +19736,56 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>130022338</v>
+        <v>130022342</v>
       </c>
       <c r="B166" t="n">
-        <v>57732</v>
+        <v>79088</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>506398</v>
+        <v>506039</v>
       </c>
       <c r="R166" t="n">
-        <v>7041609</v>
+        <v>7041535</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19819,18 +19820,39 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar, på gran.</t>
+        </is>
+      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
@@ -19848,10 +19870,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>130022334</v>
+        <v>130022264</v>
       </c>
       <c r="B167" t="n">
-        <v>91602</v>
+        <v>83059</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19859,30 +19881,26 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
@@ -19890,10 +19908,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>506052</v>
+        <v>506392</v>
       </c>
       <c r="R167" t="n">
-        <v>7041514</v>
+        <v>7041487</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19973,10 +19991,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>130022321</v>
+        <v>130022263</v>
       </c>
       <c r="B168" t="n">
-        <v>91557</v>
+        <v>83059</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19984,30 +20002,26 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>112</v>
+        <v>6440</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
@@ -20015,10 +20029,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>506094</v>
+        <v>506134</v>
       </c>
       <c r="R168" t="n">
-        <v>7041565</v>
+        <v>7041714</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20098,48 +20112,61 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>130022275</v>
+        <v>130022338</v>
       </c>
       <c r="B169" t="n">
-        <v>83059</v>
+        <v>57732</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6440</v>
+        <v>100110</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>505826</v>
+        <v>506398</v>
       </c>
       <c r="R169" t="n">
-        <v>7041551</v>
+        <v>7041609</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20180,28 +20207,12 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -20219,10 +20230,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>130022342</v>
+        <v>130022334</v>
       </c>
       <c r="B170" t="n">
-        <v>79088</v>
+        <v>91602</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20230,34 +20241,30 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
@@ -20265,10 +20272,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>506039</v>
+        <v>506052</v>
       </c>
       <c r="R170" t="n">
-        <v>7041535</v>
+        <v>7041514</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20301,11 +20308,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar, på gran.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20353,10 +20355,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>130022264</v>
+        <v>130022321</v>
       </c>
       <c r="B171" t="n">
-        <v>83059</v>
+        <v>91557</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20364,26 +20366,30 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
@@ -20391,10 +20397,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>506392</v>
+        <v>506094</v>
       </c>
       <c r="R171" t="n">
-        <v>7041487</v>
+        <v>7041565</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20474,10 +20480,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>130022263</v>
+        <v>130022339</v>
       </c>
       <c r="B172" t="n">
-        <v>83059</v>
+        <v>91626</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20485,26 +20491,26 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
@@ -20512,10 +20518,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>506134</v>
+        <v>506254</v>
       </c>
       <c r="R172" t="n">
-        <v>7041714</v>
+        <v>7041527</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20595,10 +20601,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>130022339</v>
+        <v>130022288</v>
       </c>
       <c r="B173" t="n">
-        <v>91626</v>
+        <v>57740</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20606,24 +20612,29 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N173" t="inlineStr"/>
@@ -20633,10 +20644,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>506254</v>
+        <v>506328</v>
       </c>
       <c r="R173" t="n">
-        <v>7041527</v>
+        <v>7041753</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20671,13 +20682,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55492-2025 artfynd.xlsx
+++ b/artfynd/A 55492-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129921245</v>
+        <v>129921250</v>
       </c>
       <c r="B3" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,42 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506251</v>
+        <v>506222</v>
       </c>
       <c r="R3" t="n">
-        <v>7041820</v>
+        <v>7041401</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, gamla, i gran.</t>
+          <t>På fallen, knappt levande sälg, med suraler</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129921250</v>
+        <v>129921245</v>
       </c>
       <c r="B4" t="n">
-        <v>80194</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,34 +914,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506222</v>
+        <v>506251</v>
       </c>
       <c r="R4" t="n">
-        <v>7041401</v>
+        <v>7041820</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På fallen, knappt levande sälg, med suraler</t>
+          <t>Ringhack, gamla, i gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -5502,45 +5502,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130011045</v>
+        <v>130011038</v>
       </c>
       <c r="B45" t="n">
-        <v>79088</v>
+        <v>98702</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506325</v>
+        <v>506139</v>
       </c>
       <c r="R45" t="n">
-        <v>7041726</v>
+        <v>7041442</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5577,7 +5585,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>1 vinterståndare i äldre granskog.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5586,8 +5594,14 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5604,7 +5618,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130011062</v>
+        <v>130011045</v>
       </c>
       <c r="B46" t="n">
         <v>79088</v>
@@ -5639,10 +5653,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>505881</v>
+        <v>506325</v>
       </c>
       <c r="R46" t="n">
-        <v>7041488</v>
+        <v>7041726</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5679,7 +5693,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5706,7 +5720,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130011056</v>
+        <v>130011062</v>
       </c>
       <c r="B47" t="n">
         <v>79088</v>
@@ -5741,10 +5755,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506125</v>
+        <v>505881</v>
       </c>
       <c r="R47" t="n">
-        <v>7041395</v>
+        <v>7041488</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5781,7 +5795,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5808,10 +5822,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130011040</v>
+        <v>130011056</v>
       </c>
       <c r="B48" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5819,37 +5833,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506158</v>
+        <v>506125</v>
       </c>
       <c r="R48" t="n">
-        <v>7041729</v>
+        <v>7041395</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5886,7 +5897,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Växer i en tvåstammig gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5895,34 +5906,8 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5939,42 +5924,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130011038</v>
+        <v>130011040</v>
       </c>
       <c r="B49" t="n">
-        <v>98702</v>
+        <v>91626</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220093</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5982,10 +5962,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506139</v>
+        <v>506158</v>
       </c>
       <c r="R49" t="n">
-        <v>7041442</v>
+        <v>7041729</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6022,7 +6002,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>1 vinterståndare i äldre granskog.</t>
+          <t>Växer i en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6038,6 +6018,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130011033</v>
+        <v>130011937</v>
       </c>
       <c r="B55" t="n">
-        <v>80193</v>
+        <v>91606</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6654,26 +6654,30 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6681,10 +6685,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506221</v>
+        <v>506419</v>
       </c>
       <c r="R55" t="n">
-        <v>7041401</v>
+        <v>7041521</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6719,11 +6723,6 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6741,22 +6740,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6774,61 +6768,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130011025</v>
+        <v>130011029</v>
       </c>
       <c r="B56" t="n">
-        <v>57898</v>
+        <v>97669</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506100</v>
+        <v>506106</v>
       </c>
       <c r="R56" t="n">
-        <v>7041452</v>
+        <v>7041408</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6865,7 +6847,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 2 talltitor med lockläte I äldre luckig granskog.</t>
+          <t>Rikligt i granskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6874,6 +6856,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6897,10 +6880,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130011937</v>
+        <v>130011054</v>
       </c>
       <c r="B57" t="n">
-        <v>91606</v>
+        <v>79088</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6908,41 +6891,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506419</v>
+        <v>506132</v>
       </c>
       <c r="R57" t="n">
-        <v>7041521</v>
+        <v>7041423</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6977,35 +6953,19 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7022,7 +6982,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130011054</v>
+        <v>130011053</v>
       </c>
       <c r="B58" t="n">
         <v>79088</v>
@@ -7057,10 +7017,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506132</v>
+        <v>506141</v>
       </c>
       <c r="R58" t="n">
-        <v>7041423</v>
+        <v>7041449</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7097,7 +7057,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7124,7 +7084,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130011053</v>
+        <v>130011068</v>
       </c>
       <c r="B59" t="n">
         <v>79088</v>
@@ -7159,10 +7119,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506141</v>
+        <v>505745</v>
       </c>
       <c r="R59" t="n">
-        <v>7041449</v>
+        <v>7041395</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7199,7 +7159,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7226,10 +7186,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130011068</v>
+        <v>130011033</v>
       </c>
       <c r="B60" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7237,34 +7197,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>505745</v>
+        <v>506221</v>
       </c>
       <c r="R60" t="n">
-        <v>7041395</v>
+        <v>7041401</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7301,7 +7264,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7310,8 +7273,34 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7328,49 +7317,61 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130011029</v>
+        <v>130011025</v>
       </c>
       <c r="B61" t="n">
-        <v>97669</v>
+        <v>57898</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506106</v>
+        <v>506100</v>
       </c>
       <c r="R61" t="n">
-        <v>7041408</v>
+        <v>7041452</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7407,7 +7408,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt i granskog.</t>
+          <t>Minst 2 talltitor med lockläte I äldre luckig granskog.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7416,7 +7417,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7561,10 +7561,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130011938</v>
+        <v>130011954</v>
       </c>
       <c r="B63" t="n">
-        <v>91606</v>
+        <v>79088</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7572,30 +7572,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7603,10 +7599,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506088</v>
+        <v>506077</v>
       </c>
       <c r="R63" t="n">
-        <v>7041532</v>
+        <v>7041514</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7641,6 +7637,11 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Riklig förekomst med gott om garnlavsbålar.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7654,21 +7655,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7686,10 +7672,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130011954</v>
+        <v>130011938</v>
       </c>
       <c r="B64" t="n">
-        <v>79088</v>
+        <v>91606</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7697,26 +7683,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7724,10 +7714,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506077</v>
+        <v>506088</v>
       </c>
       <c r="R64" t="n">
-        <v>7041514</v>
+        <v>7041532</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7762,11 +7752,6 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Riklig förekomst med gott om garnlavsbålar.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7780,6 +7765,21 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7928,10 +7928,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130011050</v>
+        <v>130011041</v>
       </c>
       <c r="B66" t="n">
-        <v>79088</v>
+        <v>91626</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7939,26 +7939,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7966,10 +7966,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506188</v>
+        <v>506282</v>
       </c>
       <c r="R66" t="n">
-        <v>7041400</v>
+        <v>7041798</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På bark och gren av björk i äldre granskog.</t>
+          <t>Flera fruktkroppar i en stående gran med 33 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8026,22 +8026,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8161,10 +8161,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130011041</v>
+        <v>130011020</v>
       </c>
       <c r="B68" t="n">
-        <v>91626</v>
+        <v>57740</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8172,24 +8172,29 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8199,10 +8204,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506282</v>
+        <v>506133</v>
       </c>
       <c r="R68" t="n">
-        <v>7041798</v>
+        <v>7041369</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8239,7 +8244,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående gran med 33 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8248,7 +8253,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8292,10 +8296,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130011021</v>
+        <v>130011050</v>
       </c>
       <c r="B69" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8303,31 +8307,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8335,10 +8334,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506131</v>
+        <v>506188</v>
       </c>
       <c r="R69" t="n">
-        <v>7041380</v>
+        <v>7041400</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8375,7 +8374,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran i äldre granskog.</t>
+          <t>På bark och gren av björk i äldre granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8384,6 +8383,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8394,22 +8394,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8427,7 +8427,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130011020</v>
+        <v>130011021</v>
       </c>
       <c r="B70" t="n">
         <v>57740</v>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506133</v>
+        <v>506131</v>
       </c>
       <c r="R70" t="n">
-        <v>7041369</v>
+        <v>7041380</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8562,10 +8562,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130011048</v>
+        <v>130011018</v>
       </c>
       <c r="B71" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8573,34 +8573,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506213</v>
+        <v>506297</v>
       </c>
       <c r="R71" t="n">
-        <v>7041439</v>
+        <v>7041772</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8637,7 +8645,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, längs minst 5 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8648,6 +8656,31 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8664,7 +8697,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130011957</v>
+        <v>130011048</v>
       </c>
       <c r="B72" t="n">
         <v>79088</v>
@@ -8693,19 +8726,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>505654</v>
+        <v>506213</v>
       </c>
       <c r="R72" t="n">
-        <v>7041396</v>
+        <v>7041439</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8740,20 +8770,19 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8770,10 +8799,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130011018</v>
+        <v>130011957</v>
       </c>
       <c r="B73" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8781,31 +8810,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8813,10 +8837,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506297</v>
+        <v>505654</v>
       </c>
       <c r="R73" t="n">
-        <v>7041772</v>
+        <v>7041396</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8851,43 +8875,19 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs minst 5 meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9596,7 +9596,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130011023</v>
+        <v>130011024</v>
       </c>
       <c r="B80" t="n">
         <v>57740</v>
@@ -9629,7 +9629,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505929</v>
+        <v>505908</v>
       </c>
       <c r="R80" t="n">
-        <v>7041514</v>
+        <v>7041477</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9731,10 +9731,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130011024</v>
+        <v>130011065</v>
       </c>
       <c r="B81" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9742,42 +9742,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505908</v>
+        <v>505816</v>
       </c>
       <c r="R81" t="n">
-        <v>7041477</v>
+        <v>7041475</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9814,7 +9806,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran i gammal granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9825,31 +9817,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9866,7 +9833,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130011065</v>
+        <v>130011956</v>
       </c>
       <c r="B82" t="n">
         <v>79088</v>
@@ -9895,16 +9862,19 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505816</v>
+        <v>505707</v>
       </c>
       <c r="R82" t="n">
-        <v>7041475</v>
+        <v>7041435</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9941,7 +9911,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9950,8 +9920,14 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9968,7 +9944,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130011956</v>
+        <v>130011059</v>
       </c>
       <c r="B83" t="n">
         <v>79088</v>
@@ -9997,19 +9973,16 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>505707</v>
+        <v>506131</v>
       </c>
       <c r="R83" t="n">
-        <v>7041435</v>
+        <v>7041516</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10046,7 +10019,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10055,14 +10028,8 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10079,10 +10046,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130011059</v>
+        <v>130011953</v>
       </c>
       <c r="B84" t="n">
-        <v>79088</v>
+        <v>91626</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10090,34 +10057,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506131</v>
+        <v>506196</v>
       </c>
       <c r="R84" t="n">
-        <v>7041516</v>
+        <v>7041474</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10152,19 +10122,35 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10181,7 +10167,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130011953</v>
+        <v>130011042</v>
       </c>
       <c r="B85" t="n">
         <v>91626</v>
@@ -10219,10 +10205,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506196</v>
+        <v>505757</v>
       </c>
       <c r="R85" t="n">
-        <v>7041474</v>
+        <v>7041406</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10257,6 +10243,11 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>I en klen granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10282,9 +10273,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10302,10 +10298,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130011042</v>
+        <v>130011061</v>
       </c>
       <c r="B86" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10313,37 +10309,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>505757</v>
+        <v>505949</v>
       </c>
       <c r="R86" t="n">
-        <v>7041406</v>
+        <v>7041499</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10380,7 +10373,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>I en klen granhögstubbe.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10389,34 +10382,8 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10433,10 +10400,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130011061</v>
+        <v>130011946</v>
       </c>
       <c r="B87" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10444,34 +10411,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>505949</v>
+        <v>506026</v>
       </c>
       <c r="R87" t="n">
-        <v>7041499</v>
+        <v>7041657</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10508,7 +10483,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10519,6 +10494,11 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10535,7 +10515,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130011946</v>
+        <v>130011945</v>
       </c>
       <c r="B88" t="n">
         <v>57740</v>
@@ -10578,10 +10558,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506026</v>
+        <v>506106</v>
       </c>
       <c r="R88" t="n">
-        <v>7041657</v>
+        <v>7041570</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10650,10 +10630,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130011032</v>
+        <v>130011066</v>
       </c>
       <c r="B89" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10661,41 +10641,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>506224</v>
+        <v>505790</v>
       </c>
       <c r="R89" t="n">
-        <v>7041455</v>
+        <v>7041427</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10732,7 +10705,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På en smal rönn.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10741,34 +10714,8 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10785,10 +10732,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130011066</v>
+        <v>130011032</v>
       </c>
       <c r="B90" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10796,34 +10743,41 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>505790</v>
+        <v>506224</v>
       </c>
       <c r="R90" t="n">
-        <v>7041427</v>
+        <v>7041455</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10860,7 +10814,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en smal rönn.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10869,8 +10823,34 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10887,10 +10867,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130011945</v>
+        <v>130022266</v>
       </c>
       <c r="B91" t="n">
-        <v>57740</v>
+        <v>83059</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10898,31 +10878,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10930,10 +10905,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>506106</v>
+        <v>506257</v>
       </c>
       <c r="R91" t="n">
-        <v>7041570</v>
+        <v>7041513</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10968,23 +10943,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11002,7 +10988,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130022266</v>
+        <v>130022271</v>
       </c>
       <c r="B92" t="n">
         <v>83059</v>
@@ -11040,10 +11026,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>506257</v>
+        <v>505900</v>
       </c>
       <c r="R92" t="n">
-        <v>7041513</v>
+        <v>7041531</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11123,7 +11109,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130022271</v>
+        <v>130022274</v>
       </c>
       <c r="B93" t="n">
         <v>83059</v>
@@ -11161,10 +11147,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>505900</v>
+        <v>505805</v>
       </c>
       <c r="R93" t="n">
-        <v>7041531</v>
+        <v>7041535</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11244,10 +11230,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130022274</v>
+        <v>130022345</v>
       </c>
       <c r="B94" t="n">
-        <v>83059</v>
+        <v>82925</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,21 +11241,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11282,10 +11268,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>505805</v>
+        <v>506067</v>
       </c>
       <c r="R94" t="n">
-        <v>7041535</v>
+        <v>7041537</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11365,10 +11351,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130022345</v>
+        <v>130022273</v>
       </c>
       <c r="B95" t="n">
-        <v>82925</v>
+        <v>83059</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11376,21 +11362,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11403,10 +11389,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>506067</v>
+        <v>505812</v>
       </c>
       <c r="R95" t="n">
-        <v>7041537</v>
+        <v>7041524</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11486,10 +11472,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130022273</v>
+        <v>130022295</v>
       </c>
       <c r="B96" t="n">
-        <v>83059</v>
+        <v>57740</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11497,26 +11483,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -11524,10 +11515,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>505812</v>
+        <v>506053</v>
       </c>
       <c r="R96" t="n">
-        <v>7041524</v>
+        <v>7041509</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11562,34 +11553,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11607,39 +11587,40 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130022320</v>
+        <v>130022304</v>
       </c>
       <c r="B97" t="n">
-        <v>80222</v>
+        <v>57740</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -11649,10 +11630,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>505800</v>
+        <v>505975</v>
       </c>
       <c r="R97" t="n">
-        <v>7041447</v>
+        <v>7041661</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11687,13 +11668,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11717,40 +11702,39 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130022295</v>
+        <v>130022320</v>
       </c>
       <c r="B98" t="n">
-        <v>57740</v>
+        <v>80222</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -11760,10 +11744,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>506053</v>
+        <v>505800</v>
       </c>
       <c r="R98" t="n">
-        <v>7041509</v>
+        <v>7041447</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11798,17 +11782,13 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11832,10 +11812,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130022304</v>
+        <v>130022323</v>
       </c>
       <c r="B99" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11843,16 +11823,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -11863,11 +11843,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -11875,10 +11851,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>505975</v>
+        <v>505858</v>
       </c>
       <c r="R99" t="n">
-        <v>7041661</v>
+        <v>7041579</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11915,7 +11891,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Hackspår (födosöksspår).</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11947,10 +11923,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130022323</v>
+        <v>130022287</v>
       </c>
       <c r="B100" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11958,16 +11934,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11978,7 +11954,11 @@
       <c r="I100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11986,10 +11966,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>505858</v>
+        <v>506323</v>
       </c>
       <c r="R100" t="n">
-        <v>7041579</v>
+        <v>7041761</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12026,7 +12006,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Hackspår (födosöksspår).</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12058,7 +12038,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130022287</v>
+        <v>130022289</v>
       </c>
       <c r="B101" t="n">
         <v>57740</v>
@@ -12101,10 +12081,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>506323</v>
+        <v>506341</v>
       </c>
       <c r="R101" t="n">
-        <v>7041761</v>
+        <v>7041723</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12173,10 +12153,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130022289</v>
+        <v>130022331</v>
       </c>
       <c r="B102" t="n">
-        <v>57740</v>
+        <v>78100</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12184,31 +12164,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -12216,10 +12191,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>506341</v>
+        <v>505863</v>
       </c>
       <c r="R102" t="n">
-        <v>7041723</v>
+        <v>7041558</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12254,23 +12229,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12288,10 +12274,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130022331</v>
+        <v>130011069</v>
       </c>
       <c r="B103" t="n">
-        <v>78100</v>
+        <v>79088</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12299,21 +12285,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12326,10 +12312,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>505863</v>
+        <v>505714</v>
       </c>
       <c r="R103" t="n">
-        <v>7041558</v>
+        <v>7041397</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12362,6 +12348,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12409,37 +12400,41 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130011069</v>
+        <v>130022276</v>
       </c>
       <c r="B104" t="n">
-        <v>79088</v>
+        <v>91570</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12447,10 +12442,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>505714</v>
+        <v>505821</v>
       </c>
       <c r="R104" t="n">
-        <v>7041397</v>
+        <v>7041557</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12485,11 +12480,6 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -12503,21 +12493,6 @@
       <c r="AH104" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -12535,39 +12510,40 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130022276</v>
+        <v>130022294</v>
       </c>
       <c r="B105" t="n">
-        <v>91570</v>
+        <v>57740</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -12577,10 +12553,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>505821</v>
+        <v>506049</v>
       </c>
       <c r="R105" t="n">
-        <v>7041557</v>
+        <v>7041511</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12615,13 +12591,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -12645,7 +12625,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130022294</v>
+        <v>130022290</v>
       </c>
       <c r="B106" t="n">
         <v>57740</v>
@@ -12688,10 +12668,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506049</v>
+        <v>506432</v>
       </c>
       <c r="R106" t="n">
-        <v>7041511</v>
+        <v>7041517</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12760,10 +12740,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130022290</v>
+        <v>130022328</v>
       </c>
       <c r="B107" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12771,31 +12751,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -12803,10 +12778,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>506432</v>
+        <v>505804</v>
       </c>
       <c r="R107" t="n">
-        <v>7041517</v>
+        <v>7041453</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12841,17 +12816,13 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -12875,10 +12846,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130022328</v>
+        <v>130022309</v>
       </c>
       <c r="B108" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12886,26 +12857,31 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -12913,10 +12889,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>505804</v>
+        <v>505816</v>
       </c>
       <c r="R108" t="n">
-        <v>7041453</v>
+        <v>7041559</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12951,13 +12927,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -12981,10 +12961,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130022309</v>
+        <v>130022278</v>
       </c>
       <c r="B109" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12992,29 +12972,28 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -13024,10 +13003,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>505816</v>
+        <v>506225</v>
       </c>
       <c r="R109" t="n">
-        <v>7041559</v>
+        <v>7041439</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13062,23 +13041,39 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -13217,10 +13212,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130022278</v>
+        <v>130022310</v>
       </c>
       <c r="B111" t="n">
-        <v>91606</v>
+        <v>57740</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13228,28 +13223,29 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -13259,10 +13255,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>506225</v>
+        <v>505802</v>
       </c>
       <c r="R111" t="n">
-        <v>7041439</v>
+        <v>7041546</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13297,39 +13293,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -13347,7 +13327,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130022310</v>
+        <v>130022307</v>
       </c>
       <c r="B112" t="n">
         <v>57740</v>
@@ -13380,7 +13360,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -13390,10 +13370,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>505802</v>
+        <v>505833</v>
       </c>
       <c r="R112" t="n">
-        <v>7041546</v>
+        <v>7041575</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13430,7 +13410,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13577,7 +13557,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130022307</v>
+        <v>130022298</v>
       </c>
       <c r="B114" t="n">
         <v>57740</v>
@@ -13610,7 +13590,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -13620,10 +13600,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>505833</v>
+        <v>506051</v>
       </c>
       <c r="R114" t="n">
-        <v>7041575</v>
+        <v>7041538</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13660,7 +13640,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13692,10 +13672,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130022298</v>
+        <v>130022340</v>
       </c>
       <c r="B115" t="n">
-        <v>57740</v>
+        <v>91626</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13703,29 +13683,24 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -13735,10 +13710,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>506051</v>
+        <v>506102</v>
       </c>
       <c r="R115" t="n">
-        <v>7041538</v>
+        <v>7041588</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13773,23 +13748,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -13807,10 +13793,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130022279</v>
+        <v>130022314</v>
       </c>
       <c r="B116" t="n">
-        <v>91606</v>
+        <v>57740</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13818,41 +13804,54 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>505790</v>
+        <v>505807</v>
       </c>
       <c r="R116" t="n">
-        <v>7041489</v>
+        <v>7041547</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13887,39 +13886,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Födosökande hane i en yta med mycket höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved främst av gran.</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13937,10 +13920,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130022335</v>
+        <v>130022305</v>
       </c>
       <c r="B117" t="n">
-        <v>91602</v>
+        <v>57740</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13948,28 +13931,29 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -13979,10 +13963,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>506111</v>
+        <v>505839</v>
       </c>
       <c r="R117" t="n">
-        <v>7041602</v>
+        <v>7041578</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14017,34 +14001,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14062,10 +14035,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130022322</v>
+        <v>130022301</v>
       </c>
       <c r="B118" t="n">
-        <v>91557</v>
+        <v>57740</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14073,28 +14046,29 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -14104,10 +14078,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>506082</v>
+        <v>506003</v>
       </c>
       <c r="R118" t="n">
-        <v>7041551</v>
+        <v>7041648</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14142,34 +14116,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14187,10 +14150,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130022340</v>
+        <v>130022308</v>
       </c>
       <c r="B119" t="n">
-        <v>91626</v>
+        <v>57740</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14198,24 +14161,29 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -14225,10 +14193,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>506102</v>
+        <v>505820</v>
       </c>
       <c r="R119" t="n">
-        <v>7041588</v>
+        <v>7041561</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14263,34 +14231,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -14308,10 +14265,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130022314</v>
+        <v>130022330</v>
       </c>
       <c r="B120" t="n">
-        <v>57740</v>
+        <v>78100</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14319,54 +14276,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>505807</v>
+        <v>505898</v>
       </c>
       <c r="R120" t="n">
-        <v>7041547</v>
+        <v>7041518</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14401,23 +14341,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Födosökande hane i en yta med mycket höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved främst av gran.</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14435,10 +14386,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130022305</v>
+        <v>130022279</v>
       </c>
       <c r="B121" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14446,29 +14397,28 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -14478,10 +14428,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>505839</v>
+        <v>505790</v>
       </c>
       <c r="R121" t="n">
-        <v>7041578</v>
+        <v>7041489</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14516,23 +14466,39 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14550,10 +14516,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130022301</v>
+        <v>130022335</v>
       </c>
       <c r="B122" t="n">
-        <v>57740</v>
+        <v>91602</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14561,29 +14527,28 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -14593,10 +14558,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>506003</v>
+        <v>506111</v>
       </c>
       <c r="R122" t="n">
-        <v>7041648</v>
+        <v>7041602</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14631,23 +14596,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14665,10 +14641,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130022308</v>
+        <v>130022322</v>
       </c>
       <c r="B123" t="n">
-        <v>57740</v>
+        <v>91557</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14676,29 +14652,28 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -14708,10 +14683,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>505820</v>
+        <v>506082</v>
       </c>
       <c r="R123" t="n">
-        <v>7041561</v>
+        <v>7041551</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14746,23 +14721,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -14780,10 +14766,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130022330</v>
+        <v>130022333</v>
       </c>
       <c r="B124" t="n">
-        <v>78100</v>
+        <v>91602</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14791,26 +14777,30 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -14818,10 +14808,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>505898</v>
+        <v>506291</v>
       </c>
       <c r="R124" t="n">
-        <v>7041518</v>
+        <v>7041817</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14901,7 +14891,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130022333</v>
+        <v>130022336</v>
       </c>
       <c r="B125" t="n">
         <v>91602</v>
@@ -14943,10 +14933,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>506291</v>
+        <v>505807</v>
       </c>
       <c r="R125" t="n">
-        <v>7041817</v>
+        <v>7041535</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15026,10 +15016,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130022336</v>
+        <v>130022300</v>
       </c>
       <c r="B126" t="n">
-        <v>91602</v>
+        <v>57740</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15037,28 +15027,29 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -15068,10 +15059,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>505807</v>
+        <v>506005</v>
       </c>
       <c r="R126" t="n">
-        <v>7041535</v>
+        <v>7041651</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15106,34 +15097,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -15151,10 +15131,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130022349</v>
+        <v>130022306</v>
       </c>
       <c r="B127" t="n">
-        <v>83051</v>
+        <v>57740</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15162,26 +15142,31 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -15189,10 +15174,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>505803</v>
+        <v>505833</v>
       </c>
       <c r="R127" t="n">
-        <v>7041538</v>
+        <v>7041571</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15227,13 +15212,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -15257,10 +15246,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130022265</v>
+        <v>130022349</v>
       </c>
       <c r="B128" t="n">
-        <v>83059</v>
+        <v>83051</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15268,21 +15257,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15295,10 +15284,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>506287</v>
+        <v>505803</v>
       </c>
       <c r="R128" t="n">
-        <v>7041437</v>
+        <v>7041538</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15346,21 +15335,6 @@
       <c r="AH128" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -15378,7 +15352,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130022267</v>
+        <v>130022265</v>
       </c>
       <c r="B129" t="n">
         <v>83059</v>
@@ -15416,10 +15390,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>506213</v>
+        <v>506287</v>
       </c>
       <c r="R129" t="n">
-        <v>7041527</v>
+        <v>7041437</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15499,7 +15473,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130022272</v>
+        <v>130022267</v>
       </c>
       <c r="B130" t="n">
         <v>83059</v>
@@ -15537,10 +15511,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>505861</v>
+        <v>506213</v>
       </c>
       <c r="R130" t="n">
-        <v>7041553</v>
+        <v>7041527</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15620,10 +15594,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130022300</v>
+        <v>130022272</v>
       </c>
       <c r="B131" t="n">
-        <v>57740</v>
+        <v>83059</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15631,31 +15605,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
@@ -15663,10 +15632,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>506005</v>
+        <v>505861</v>
       </c>
       <c r="R131" t="n">
-        <v>7041651</v>
+        <v>7041553</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15701,23 +15670,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15735,40 +15715,39 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130022306</v>
+        <v>130022282</v>
       </c>
       <c r="B132" t="n">
-        <v>57740</v>
+        <v>92324</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -15778,10 +15757,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>505833</v>
+        <v>505786</v>
       </c>
       <c r="R132" t="n">
-        <v>7041571</v>
+        <v>7041510</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15816,17 +15795,13 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -15980,10 +15955,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130022317</v>
+        <v>130022293</v>
       </c>
       <c r="B134" t="n">
-        <v>57898</v>
+        <v>57740</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15991,50 +15966,42 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>505940</v>
+        <v>506204</v>
       </c>
       <c r="R134" t="n">
-        <v>7041639</v>
+        <v>7041525</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16069,6 +16036,11 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -16081,11 +16053,6 @@
       <c r="AH134" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>Flerskiktad skog i många delar.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -16103,39 +16070,40 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130022282</v>
+        <v>130022283</v>
       </c>
       <c r="B135" t="n">
-        <v>92324</v>
+        <v>57740</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -16145,10 +16113,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>505786</v>
+        <v>506152</v>
       </c>
       <c r="R135" t="n">
-        <v>7041510</v>
+        <v>7041714</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16183,13 +16151,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -16213,10 +16185,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130022293</v>
+        <v>130022317</v>
       </c>
       <c r="B136" t="n">
-        <v>57740</v>
+        <v>57898</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16224,42 +16196,50 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>506204</v>
+        <v>505940</v>
       </c>
       <c r="R136" t="n">
-        <v>7041525</v>
+        <v>7041639</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16294,11 +16274,6 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -16311,6 +16286,11 @@
       <c r="AH136" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>Flerskiktad skog i många delar.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -16328,10 +16308,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130022283</v>
+        <v>130022347</v>
       </c>
       <c r="B137" t="n">
-        <v>57740</v>
+        <v>82925</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16339,42 +16319,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>506152</v>
+        <v>505809</v>
       </c>
       <c r="R137" t="n">
-        <v>7041714</v>
+        <v>7041517</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16409,11 +16381,6 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
@@ -16422,11 +16389,6 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
@@ -16443,10 +16405,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130022347</v>
+        <v>130022316</v>
       </c>
       <c r="B138" t="n">
-        <v>82925</v>
+        <v>57898</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16454,34 +16416,50 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>505809</v>
+        <v>506108</v>
       </c>
       <c r="R138" t="n">
-        <v>7041517</v>
+        <v>7041591</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16524,6 +16502,11 @@
       </c>
       <c r="AG138" t="b">
         <v>0</v>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
@@ -16540,61 +16523,48 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130022316</v>
+        <v>130022350</v>
       </c>
       <c r="B139" t="n">
-        <v>57898</v>
+        <v>79344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>103021</v>
+        <v>6459</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>506108</v>
+        <v>505800</v>
       </c>
       <c r="R139" t="n">
-        <v>7041591</v>
+        <v>7041447</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16635,12 +16605,18 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av björk, sälg och rönn.</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -16888,37 +16864,42 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130022350</v>
+        <v>130022291</v>
       </c>
       <c r="B142" t="n">
-        <v>79344</v>
+        <v>57740</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -16926,10 +16907,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>505800</v>
+        <v>506255</v>
       </c>
       <c r="R142" t="n">
-        <v>7041447</v>
+        <v>7041529</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16964,13 +16945,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Gammalt bohål (45mm i diameter) i grantickerötad granshögtubbe, beläget ca 2 meter upp i högstubben.</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -16979,9 +16964,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av björk, sälg och rönn.</t>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -17129,7 +17129,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130022291</v>
+        <v>130022292</v>
       </c>
       <c r="B144" t="n">
         <v>57740</v>
@@ -17162,7 +17162,7 @@
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -17172,10 +17172,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>506255</v>
+        <v>506242</v>
       </c>
       <c r="R144" t="n">
-        <v>7041529</v>
+        <v>7041507</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17212,7 +17212,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Gammalt bohål (45mm i diameter) i grantickerötad granshögtubbe, beläget ca 2 meter upp i högstubben.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17227,26 +17227,6 @@
       <c r="AH144" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -17264,7 +17244,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130022292</v>
+        <v>130022299</v>
       </c>
       <c r="B145" t="n">
         <v>57740</v>
@@ -17307,10 +17287,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>506242</v>
+        <v>506050</v>
       </c>
       <c r="R145" t="n">
-        <v>7041507</v>
+        <v>7041531</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17379,7 +17359,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130022299</v>
+        <v>130022286</v>
       </c>
       <c r="B146" t="n">
         <v>57740</v>
@@ -17422,10 +17402,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>506050</v>
+        <v>506315</v>
       </c>
       <c r="R146" t="n">
-        <v>7041531</v>
+        <v>7041762</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17494,10 +17474,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130022286</v>
+        <v>130022332</v>
       </c>
       <c r="B147" t="n">
-        <v>57740</v>
+        <v>56921</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17505,16 +17485,16 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -17522,25 +17502,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>506315</v>
+        <v>505757</v>
       </c>
       <c r="R147" t="n">
-        <v>7041762</v>
+        <v>7041488</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17573,11 +17561,6 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17836,10 +17819,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130022332</v>
+        <v>130022296</v>
       </c>
       <c r="B150" t="n">
-        <v>56921</v>
+        <v>57740</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17847,16 +17830,16 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -17864,33 +17847,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>505757</v>
+        <v>506041</v>
       </c>
       <c r="R150" t="n">
-        <v>7041488</v>
+        <v>7041525</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17923,6 +17898,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17954,10 +17934,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130022344</v>
+        <v>130022313</v>
       </c>
       <c r="B151" t="n">
-        <v>82925</v>
+        <v>57740</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17965,26 +17945,31 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -17992,10 +17977,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>506043</v>
+        <v>505812</v>
       </c>
       <c r="R151" t="n">
-        <v>7041532</v>
+        <v>7041551</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18030,34 +18015,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -18075,10 +18049,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130022337</v>
+        <v>130022297</v>
       </c>
       <c r="B152" t="n">
-        <v>91620</v>
+        <v>57740</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18086,28 +18060,29 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -18117,10 +18092,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>505832</v>
+        <v>506062</v>
       </c>
       <c r="R152" t="n">
-        <v>7041497</v>
+        <v>7041558</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18155,13 +18130,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -18185,7 +18164,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130022346</v>
+        <v>130022344</v>
       </c>
       <c r="B153" t="n">
         <v>82925</v>
@@ -18223,10 +18202,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>505969</v>
+        <v>506043</v>
       </c>
       <c r="R153" t="n">
-        <v>7041653</v>
+        <v>7041532</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18306,10 +18285,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130022269</v>
+        <v>130022337</v>
       </c>
       <c r="B154" t="n">
-        <v>83059</v>
+        <v>91620</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18317,26 +18296,30 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
@@ -18344,10 +18327,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>506062</v>
+        <v>505832</v>
       </c>
       <c r="R154" t="n">
-        <v>7041545</v>
+        <v>7041497</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18395,21 +18378,6 @@
       <c r="AH154" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -18427,10 +18395,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130022296</v>
+        <v>130022346</v>
       </c>
       <c r="B155" t="n">
-        <v>57740</v>
+        <v>82925</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18438,31 +18406,26 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -18470,10 +18433,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>506041</v>
+        <v>505969</v>
       </c>
       <c r="R155" t="n">
-        <v>7041525</v>
+        <v>7041653</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18508,23 +18471,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>
@@ -18542,10 +18516,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130022313</v>
+        <v>130022270</v>
       </c>
       <c r="B156" t="n">
-        <v>57740</v>
+        <v>83059</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18553,31 +18527,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -18585,10 +18554,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>505812</v>
+        <v>505972</v>
       </c>
       <c r="R156" t="n">
-        <v>7041551</v>
+        <v>7041657</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18623,23 +18592,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -18657,10 +18637,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130022297</v>
+        <v>130022318</v>
       </c>
       <c r="B157" t="n">
-        <v>57740</v>
+        <v>57898</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18668,42 +18648,50 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>506062</v>
+        <v>505748</v>
       </c>
       <c r="R157" t="n">
-        <v>7041558</v>
+        <v>7041442</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18736,11 +18724,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18772,10 +18755,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130022318</v>
+        <v>130022269</v>
       </c>
       <c r="B158" t="n">
-        <v>57898</v>
+        <v>83059</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18783,50 +18766,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>505748</v>
+        <v>506062</v>
       </c>
       <c r="R158" t="n">
-        <v>7041442</v>
+        <v>7041545</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18867,12 +18837,28 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -18890,32 +18876,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130022270</v>
+        <v>130022324</v>
       </c>
       <c r="B159" t="n">
-        <v>83059</v>
+        <v>83057</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6440</v>
+        <v>6486</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18928,10 +18914,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>505972</v>
+        <v>505884</v>
       </c>
       <c r="R159" t="n">
-        <v>7041657</v>
+        <v>7041508</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18991,9 +18977,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>
@@ -19011,10 +19002,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130022324</v>
+        <v>130022319</v>
       </c>
       <c r="B160" t="n">
-        <v>83057</v>
+        <v>58375</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19022,37 +19013,50 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6486</v>
+        <v>102125</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>505884</v>
+        <v>505775</v>
       </c>
       <c r="R160" t="n">
-        <v>7041508</v>
+        <v>7041440</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19087,39 +19091,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Observerades i gammal grandominerad skog med inslag av björk och enstaka sälg och rönn.</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -19137,61 +19125,52 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130022319</v>
+        <v>130022281</v>
       </c>
       <c r="B161" t="n">
-        <v>58375</v>
+        <v>92324</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>102125</v>
+        <v>3298</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>505775</v>
+        <v>506113</v>
       </c>
       <c r="R161" t="n">
-        <v>7041440</v>
+        <v>7041592</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19226,17 +19205,13 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Observerades i gammal grandominerad skog med inslag av björk och enstaka sälg och rönn.</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -19260,39 +19235,40 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>130022281</v>
+        <v>130022312</v>
       </c>
       <c r="B162" t="n">
-        <v>92324</v>
+        <v>57740</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -19302,10 +19278,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>506113</v>
+        <v>505809</v>
       </c>
       <c r="R162" t="n">
-        <v>7041592</v>
+        <v>7041553</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19340,13 +19316,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -19370,7 +19350,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>130022312</v>
+        <v>130022315</v>
       </c>
       <c r="B163" t="n">
         <v>57740</v>
@@ -19403,7 +19383,7 @@
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -19413,10 +19393,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>505809</v>
+        <v>505763</v>
       </c>
       <c r="R163" t="n">
-        <v>7041553</v>
+        <v>7041524</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19453,7 +19433,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19468,6 +19448,21 @@
       <c r="AH163" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -19485,53 +19480,61 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130022315</v>
+        <v>130022338</v>
       </c>
       <c r="B164" t="n">
-        <v>57740</v>
+        <v>57732</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>505763</v>
+        <v>506398</v>
       </c>
       <c r="R164" t="n">
-        <v>7041524</v>
+        <v>7041609</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19566,11 +19569,6 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
@@ -19583,21 +19581,6 @@
       <c r="AH164" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -19615,10 +19598,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130022275</v>
+        <v>130022334</v>
       </c>
       <c r="B165" t="n">
-        <v>83059</v>
+        <v>91602</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19626,26 +19609,30 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
@@ -19653,10 +19640,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>505826</v>
+        <v>506052</v>
       </c>
       <c r="R165" t="n">
-        <v>7041551</v>
+        <v>7041514</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19736,10 +19723,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>130022342</v>
+        <v>130022321</v>
       </c>
       <c r="B166" t="n">
-        <v>79088</v>
+        <v>91557</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19747,34 +19734,30 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
@@ -19782,10 +19765,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>506039</v>
+        <v>506094</v>
       </c>
       <c r="R166" t="n">
-        <v>7041535</v>
+        <v>7041565</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19818,11 +19801,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar, på gran.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19870,7 +19848,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>130022264</v>
+        <v>130022275</v>
       </c>
       <c r="B167" t="n">
         <v>83059</v>
@@ -19908,10 +19886,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>506392</v>
+        <v>505826</v>
       </c>
       <c r="R167" t="n">
-        <v>7041487</v>
+        <v>7041551</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19991,10 +19969,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>130022263</v>
+        <v>130022342</v>
       </c>
       <c r="B168" t="n">
-        <v>83059</v>
+        <v>79088</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20002,25 +19980,33 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
@@ -20029,10 +20015,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>506134</v>
+        <v>506039</v>
       </c>
       <c r="R168" t="n">
-        <v>7041714</v>
+        <v>7041535</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20065,6 +20051,11 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar, på gran.</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20112,61 +20103,48 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>130022338</v>
+        <v>130022264</v>
       </c>
       <c r="B169" t="n">
-        <v>57732</v>
+        <v>83059</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100110</v>
+        <v>6440</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>506398</v>
+        <v>506392</v>
       </c>
       <c r="R169" t="n">
-        <v>7041609</v>
+        <v>7041487</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20207,12 +20185,28 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -20230,10 +20224,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>130022334</v>
+        <v>130022263</v>
       </c>
       <c r="B170" t="n">
-        <v>91602</v>
+        <v>83059</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20241,30 +20235,26 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
@@ -20272,10 +20262,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>506052</v>
+        <v>506134</v>
       </c>
       <c r="R170" t="n">
-        <v>7041514</v>
+        <v>7041714</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20355,10 +20345,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>130022321</v>
+        <v>130022339</v>
       </c>
       <c r="B171" t="n">
-        <v>91557</v>
+        <v>91626</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20366,23 +20356,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Pat.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
@@ -20397,10 +20383,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>506094</v>
+        <v>506254</v>
       </c>
       <c r="R171" t="n">
-        <v>7041565</v>
+        <v>7041527</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20480,10 +20466,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>130022339</v>
+        <v>130022288</v>
       </c>
       <c r="B172" t="n">
-        <v>91626</v>
+        <v>57740</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20491,24 +20477,29 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
@@ -20518,10 +20509,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>506254</v>
+        <v>506328</v>
       </c>
       <c r="R172" t="n">
-        <v>7041527</v>
+        <v>7041753</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20556,13 +20547,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -20601,7 +20596,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>130022288</v>
+        <v>130011023</v>
       </c>
       <c r="B173" t="n">
         <v>57740</v>
@@ -20644,10 +20639,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>506328</v>
+        <v>505929</v>
       </c>
       <c r="R173" t="n">
-        <v>7041753</v>
+        <v>7041514</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20684,7 +20679,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20711,9 +20706,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>

--- a/artfynd/A 55492-2025 artfynd.xlsx
+++ b/artfynd/A 55492-2025 artfynd.xlsx
@@ -4739,45 +4739,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130011049</v>
+        <v>130011939</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>92357</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506235</v>
+        <v>506013</v>
       </c>
       <c r="R38" t="n">
-        <v>7041415</v>
+        <v>7041655</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4812,19 +4819,35 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4956,7 +4979,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130011044</v>
+        <v>130011049</v>
       </c>
       <c r="B40" t="n">
         <v>79095</v>
@@ -4991,10 +5014,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506151</v>
+        <v>506235</v>
       </c>
       <c r="R40" t="n">
-        <v>7041726</v>
+        <v>7041415</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5031,7 +5054,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5058,7 +5081,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130011060</v>
+        <v>130011044</v>
       </c>
       <c r="B41" t="n">
         <v>79095</v>
@@ -5093,10 +5116,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>505941</v>
+        <v>506151</v>
       </c>
       <c r="R41" t="n">
-        <v>7041526</v>
+        <v>7041726</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5160,7 +5183,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130011064</v>
+        <v>130011060</v>
       </c>
       <c r="B42" t="n">
         <v>79095</v>
@@ -5195,10 +5218,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>505859</v>
+        <v>505941</v>
       </c>
       <c r="R42" t="n">
-        <v>7041479</v>
+        <v>7041526</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5262,52 +5285,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130011939</v>
+        <v>130011064</v>
       </c>
       <c r="B43" t="n">
-        <v>92357</v>
+        <v>79095</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506013</v>
+        <v>505859</v>
       </c>
       <c r="R43" t="n">
-        <v>7041655</v>
+        <v>7041479</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5342,35 +5358,19 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -11351,37 +11351,41 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130022345</v>
+        <v>130022320</v>
       </c>
       <c r="B95" t="n">
-        <v>82939</v>
+        <v>80229</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11389,10 +11393,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>506067</v>
+        <v>505800</v>
       </c>
       <c r="R95" t="n">
-        <v>7041537</v>
+        <v>7041447</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11440,21 +11444,6 @@
       <c r="AH95" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11472,10 +11461,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130022295</v>
+        <v>130022345</v>
       </c>
       <c r="B96" t="n">
-        <v>57741</v>
+        <v>82939</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11483,31 +11472,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -11515,10 +11499,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>506053</v>
+        <v>506067</v>
       </c>
       <c r="R96" t="n">
-        <v>7041509</v>
+        <v>7041537</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11553,23 +11537,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11587,7 +11582,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130022304</v>
+        <v>130022295</v>
       </c>
       <c r="B97" t="n">
         <v>57741</v>
@@ -11630,10 +11625,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>505975</v>
+        <v>506053</v>
       </c>
       <c r="R97" t="n">
-        <v>7041661</v>
+        <v>7041509</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11702,39 +11697,40 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130022320</v>
+        <v>130022304</v>
       </c>
       <c r="B98" t="n">
-        <v>80229</v>
+        <v>57741</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -11744,10 +11740,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>505800</v>
+        <v>505975</v>
       </c>
       <c r="R98" t="n">
-        <v>7041447</v>
+        <v>7041661</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11782,13 +11778,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -12038,10 +12038,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130011069</v>
+        <v>130022331</v>
       </c>
       <c r="B101" t="n">
-        <v>79095</v>
+        <v>78107</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12049,21 +12049,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>505714</v>
+        <v>505863</v>
       </c>
       <c r="R101" t="n">
-        <v>7041397</v>
+        <v>7041558</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12112,11 +12112,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12164,39 +12159,40 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130022276</v>
+        <v>130022289</v>
       </c>
       <c r="B102" t="n">
-        <v>91603</v>
+        <v>57741</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -12206,10 +12202,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>505821</v>
+        <v>506341</v>
       </c>
       <c r="R102" t="n">
-        <v>7041557</v>
+        <v>7041723</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12244,13 +12240,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130022290</v>
+        <v>130022294</v>
       </c>
       <c r="B103" t="n">
         <v>57741</v>
@@ -12317,10 +12317,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>506432</v>
+        <v>506049</v>
       </c>
       <c r="R103" t="n">
-        <v>7041517</v>
+        <v>7041511</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12389,10 +12389,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130022289</v>
+        <v>130011069</v>
       </c>
       <c r="B104" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12400,31 +12400,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12432,10 +12427,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>506341</v>
+        <v>505714</v>
       </c>
       <c r="R104" t="n">
-        <v>7041723</v>
+        <v>7041397</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12472,7 +12467,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12481,12 +12476,28 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -12504,40 +12515,39 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130022294</v>
+        <v>130022276</v>
       </c>
       <c r="B105" t="n">
-        <v>57741</v>
+        <v>91603</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -12547,10 +12557,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>506049</v>
+        <v>505821</v>
       </c>
       <c r="R105" t="n">
-        <v>7041511</v>
+        <v>7041557</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12585,17 +12595,13 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -12619,10 +12625,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130022331</v>
+        <v>130022290</v>
       </c>
       <c r="B106" t="n">
-        <v>78107</v>
+        <v>57741</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12630,26 +12636,31 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -12657,10 +12668,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>505863</v>
+        <v>506432</v>
       </c>
       <c r="R106" t="n">
-        <v>7041558</v>
+        <v>7041517</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12695,34 +12706,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -13672,10 +13672,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130022330</v>
+        <v>130022305</v>
       </c>
       <c r="B115" t="n">
-        <v>78107</v>
+        <v>57741</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13683,26 +13683,31 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -13710,10 +13715,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>505898</v>
+        <v>505839</v>
       </c>
       <c r="R115" t="n">
-        <v>7041518</v>
+        <v>7041578</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13748,34 +13753,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -13793,10 +13787,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130022322</v>
+        <v>130022301</v>
       </c>
       <c r="B116" t="n">
-        <v>91590</v>
+        <v>57741</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13804,28 +13798,29 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -13835,10 +13830,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>506082</v>
+        <v>506003</v>
       </c>
       <c r="R116" t="n">
-        <v>7041551</v>
+        <v>7041648</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13873,34 +13868,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13918,10 +13902,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130022279</v>
+        <v>130022308</v>
       </c>
       <c r="B117" t="n">
-        <v>91639</v>
+        <v>57741</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13929,28 +13913,29 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -13960,10 +13945,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>505790</v>
+        <v>505820</v>
       </c>
       <c r="R117" t="n">
-        <v>7041489</v>
+        <v>7041561</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13998,39 +13983,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14048,10 +14017,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130022335</v>
+        <v>130022314</v>
       </c>
       <c r="B118" t="n">
-        <v>91635</v>
+        <v>57741</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14059,41 +14028,54 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>506111</v>
+        <v>505807</v>
       </c>
       <c r="R118" t="n">
-        <v>7041602</v>
+        <v>7041547</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14128,34 +14110,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Födosökande hane i en yta med mycket höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved främst av gran.</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14173,10 +14144,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130022340</v>
+        <v>130022330</v>
       </c>
       <c r="B119" t="n">
-        <v>91659</v>
+        <v>78107</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14184,26 +14155,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -14211,10 +14182,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>506102</v>
+        <v>505898</v>
       </c>
       <c r="R119" t="n">
-        <v>7041588</v>
+        <v>7041518</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14294,10 +14265,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130022305</v>
+        <v>130022322</v>
       </c>
       <c r="B120" t="n">
-        <v>57741</v>
+        <v>91590</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14305,29 +14276,28 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -14337,10 +14307,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>505839</v>
+        <v>506082</v>
       </c>
       <c r="R120" t="n">
-        <v>7041578</v>
+        <v>7041551</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14375,23 +14345,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14409,10 +14390,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130022301</v>
+        <v>130022279</v>
       </c>
       <c r="B121" t="n">
-        <v>57741</v>
+        <v>91639</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14420,29 +14401,28 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -14452,10 +14432,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>506003</v>
+        <v>505790</v>
       </c>
       <c r="R121" t="n">
-        <v>7041648</v>
+        <v>7041489</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14490,23 +14470,39 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14524,10 +14520,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130022308</v>
+        <v>130022335</v>
       </c>
       <c r="B122" t="n">
-        <v>57741</v>
+        <v>91635</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14535,29 +14531,28 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -14567,10 +14562,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>505820</v>
+        <v>506111</v>
       </c>
       <c r="R122" t="n">
-        <v>7041561</v>
+        <v>7041602</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14605,23 +14600,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14639,10 +14645,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130022314</v>
+        <v>130022340</v>
       </c>
       <c r="B123" t="n">
-        <v>57741</v>
+        <v>91659</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14650,54 +14656,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>505807</v>
+        <v>506102</v>
       </c>
       <c r="R123" t="n">
-        <v>7041547</v>
+        <v>7041588</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14732,23 +14721,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Födosökande hane i en yta med mycket höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved främst av gran.</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -15715,32 +15715,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130022282</v>
+        <v>130022280</v>
       </c>
       <c r="B132" t="n">
-        <v>92357</v>
+        <v>91639</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15757,10 +15757,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>505786</v>
+        <v>505798</v>
       </c>
       <c r="R132" t="n">
-        <v>7041510</v>
+        <v>7041503</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15808,6 +15808,26 @@
       <c r="AH132" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15825,40 +15845,39 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130022293</v>
+        <v>130022282</v>
       </c>
       <c r="B133" t="n">
-        <v>57741</v>
+        <v>92357</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -15868,10 +15887,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>506204</v>
+        <v>505786</v>
       </c>
       <c r="R133" t="n">
-        <v>7041525</v>
+        <v>7041510</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15906,17 +15925,13 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -15940,7 +15955,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130022283</v>
+        <v>130022293</v>
       </c>
       <c r="B134" t="n">
         <v>57741</v>
@@ -15983,10 +15998,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>506152</v>
+        <v>506204</v>
       </c>
       <c r="R134" t="n">
-        <v>7041714</v>
+        <v>7041525</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16055,10 +16070,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130022317</v>
+        <v>130022283</v>
       </c>
       <c r="B135" t="n">
-        <v>57900</v>
+        <v>57741</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16066,50 +16081,42 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>505940</v>
+        <v>506152</v>
       </c>
       <c r="R135" t="n">
-        <v>7041639</v>
+        <v>7041714</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16144,6 +16151,11 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -16156,11 +16168,6 @@
       <c r="AH135" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>Flerskiktad skog i många delar.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -16178,10 +16185,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130022280</v>
+        <v>130022317</v>
       </c>
       <c r="B136" t="n">
-        <v>91639</v>
+        <v>57900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16189,41 +16196,50 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>505798</v>
+        <v>505940</v>
       </c>
       <c r="R136" t="n">
-        <v>7041503</v>
+        <v>7041639</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16264,7 +16280,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -16273,24 +16288,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>Flerskiktad skog i många delar.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -16308,10 +16308,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130022316</v>
+        <v>130022347</v>
       </c>
       <c r="B137" t="n">
-        <v>57900</v>
+        <v>82939</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16319,50 +16319,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>506108</v>
+        <v>505809</v>
       </c>
       <c r="R137" t="n">
-        <v>7041591</v>
+        <v>7041517</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16405,11 +16389,6 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
@@ -16426,10 +16405,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130022347</v>
+        <v>130022316</v>
       </c>
       <c r="B138" t="n">
-        <v>82939</v>
+        <v>57900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16437,34 +16416,50 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>505809</v>
+        <v>506108</v>
       </c>
       <c r="R138" t="n">
-        <v>7041517</v>
+        <v>7041591</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16507,6 +16502,11 @@
       </c>
       <c r="AG138" t="b">
         <v>0</v>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
@@ -18413,10 +18413,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130022296</v>
+        <v>130022318</v>
       </c>
       <c r="B155" t="n">
-        <v>57741</v>
+        <v>57900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18424,42 +18424,50 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>506041</v>
+        <v>505748</v>
       </c>
       <c r="R155" t="n">
-        <v>7041525</v>
+        <v>7041442</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18492,11 +18500,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18528,7 +18531,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130022297</v>
+        <v>130022296</v>
       </c>
       <c r="B156" t="n">
         <v>57741</v>
@@ -18571,10 +18574,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>506062</v>
+        <v>506041</v>
       </c>
       <c r="R156" t="n">
-        <v>7041558</v>
+        <v>7041525</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18643,7 +18646,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130022313</v>
+        <v>130022297</v>
       </c>
       <c r="B157" t="n">
         <v>57741</v>
@@ -18686,10 +18689,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>505812</v>
+        <v>506062</v>
       </c>
       <c r="R157" t="n">
-        <v>7041551</v>
+        <v>7041558</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18758,10 +18761,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130022318</v>
+        <v>130022313</v>
       </c>
       <c r="B158" t="n">
-        <v>57900</v>
+        <v>57741</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18769,50 +18772,42 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>505748</v>
+        <v>505812</v>
       </c>
       <c r="R158" t="n">
-        <v>7041442</v>
+        <v>7041551</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18845,6 +18840,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19977,10 +19977,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>130022321</v>
+        <v>130022334</v>
       </c>
       <c r="B168" t="n">
-        <v>91590</v>
+        <v>91635</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19988,21 +19988,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>112</v>
+        <v>1108</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -20019,10 +20019,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>506094</v>
+        <v>506052</v>
       </c>
       <c r="R168" t="n">
-        <v>7041565</v>
+        <v>7041514</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20102,10 +20102,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>130022334</v>
+        <v>130022339</v>
       </c>
       <c r="B169" t="n">
-        <v>91635</v>
+        <v>91659</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20113,23 +20113,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
@@ -20144,10 +20140,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>506052</v>
+        <v>506254</v>
       </c>
       <c r="R169" t="n">
-        <v>7041514</v>
+        <v>7041527</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20227,61 +20223,52 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>130022338</v>
+        <v>130022321</v>
       </c>
       <c r="B170" t="n">
-        <v>57733</v>
+        <v>91590</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100110</v>
+        <v>112</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>506398</v>
+        <v>506094</v>
       </c>
       <c r="R170" t="n">
-        <v>7041609</v>
+        <v>7041565</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20322,12 +20309,28 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -20345,48 +20348,61 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>130022339</v>
+        <v>130022338</v>
       </c>
       <c r="B171" t="n">
-        <v>91659</v>
+        <v>57733</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5432</v>
+        <v>100110</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>506254</v>
+        <v>506398</v>
       </c>
       <c r="R171" t="n">
-        <v>7041527</v>
+        <v>7041609</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20427,28 +20443,12 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>

--- a/artfynd/A 55492-2025 artfynd.xlsx
+++ b/artfynd/A 55492-2025 artfynd.xlsx
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129921246</v>
+        <v>129921258</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,42 +1024,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505962</v>
+        <v>506384</v>
       </c>
       <c r="R5" t="n">
-        <v>7041505</v>
+        <v>7041622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129921258</v>
+        <v>129921257</v>
       </c>
       <c r="B6" t="n">
         <v>79095</v>
@@ -1158,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506384</v>
+        <v>506139</v>
       </c>
       <c r="R6" t="n">
-        <v>7041622</v>
+        <v>7041701</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129921257</v>
+        <v>129921246</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,34 +1228,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506139</v>
+        <v>505962</v>
       </c>
       <c r="R7" t="n">
-        <v>7041701</v>
+        <v>7041505</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -3213,39 +3213,40 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130011936</v>
+        <v>130011943</v>
       </c>
       <c r="B25" t="n">
-        <v>91603</v>
+        <v>57741</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3255,10 +3256,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506219</v>
+        <v>506047</v>
       </c>
       <c r="R25" t="n">
-        <v>7041490</v>
+        <v>7041498</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3293,13 +3294,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3323,7 +3328,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130011943</v>
+        <v>130011947</v>
       </c>
       <c r="B26" t="n">
         <v>57741</v>
@@ -3356,7 +3361,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3366,10 +3371,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506047</v>
+        <v>505728</v>
       </c>
       <c r="R26" t="n">
-        <v>7041498</v>
+        <v>7041430</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3406,7 +3411,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3438,7 +3443,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130011947</v>
+        <v>130011022</v>
       </c>
       <c r="B27" t="n">
         <v>57741</v>
@@ -3481,10 +3486,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505728</v>
+        <v>506105</v>
       </c>
       <c r="R27" t="n">
-        <v>7041430</v>
+        <v>7041429</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3521,7 +3526,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3536,6 +3541,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3553,40 +3578,39 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130011022</v>
+        <v>130011936</v>
       </c>
       <c r="B28" t="n">
-        <v>57741</v>
+        <v>91603</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3596,10 +3620,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506105</v>
+        <v>506219</v>
       </c>
       <c r="R28" t="n">
-        <v>7041429</v>
+        <v>7041490</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3634,43 +3658,19 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130011051</v>
+        <v>130011027</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3814,34 +3814,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506173</v>
+        <v>505811</v>
       </c>
       <c r="R30" t="n">
-        <v>7041436</v>
+        <v>7041517</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3878,7 +3886,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>Rejäla äldre hackspår i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,6 +3897,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3905,10 +3938,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130011027</v>
+        <v>130011959</v>
       </c>
       <c r="B31" t="n">
-        <v>57738</v>
+        <v>82939</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3916,42 +3949,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505811</v>
+        <v>505869</v>
       </c>
       <c r="R31" t="n">
-        <v>7041517</v>
+        <v>7041576</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3986,17 +4011,13 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rejäla äldre hackspår i en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4015,14 +4036,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4040,10 +4056,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130011959</v>
+        <v>130011051</v>
       </c>
       <c r="B32" t="n">
-        <v>82939</v>
+        <v>79095</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4051,21 +4067,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4075,10 +4091,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505869</v>
+        <v>506173</v>
       </c>
       <c r="R32" t="n">
-        <v>7041576</v>
+        <v>7041436</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4113,35 +4129,19 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På flera granar i granskog.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4158,27 +4158,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130011036</v>
+        <v>130011948</v>
       </c>
       <c r="B33" t="n">
-        <v>57845</v>
+        <v>57741</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4186,33 +4186,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>505812</v>
+        <v>505728</v>
       </c>
       <c r="R33" t="n">
-        <v>7041524</v>
+        <v>7041439</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4249,7 +4241,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>2 nyfikna lavskrikor med lockläte i flerskiktad granskog med bitvis rikligt med garnlav på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4281,48 +4273,61 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130011955</v>
+        <v>130011036</v>
       </c>
       <c r="B34" t="n">
-        <v>79095</v>
+        <v>57845</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506094</v>
+        <v>505812</v>
       </c>
       <c r="R34" t="n">
-        <v>7041562</v>
+        <v>7041524</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4359,7 +4364,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>2 nyfikna lavskrikor med lockläte i flerskiktad granskog med bitvis rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4368,7 +4373,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4392,7 +4396,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130011058</v>
+        <v>130011955</v>
       </c>
       <c r="B35" t="n">
         <v>79095</v>
@@ -4421,16 +4425,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506127</v>
+        <v>506094</v>
       </c>
       <c r="R35" t="n">
-        <v>7041473</v>
+        <v>7041562</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4467,7 +4474,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4476,8 +4483,14 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4494,10 +4507,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130011948</v>
+        <v>130011058</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4505,42 +4518,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505728</v>
+        <v>506127</v>
       </c>
       <c r="R36" t="n">
-        <v>7041439</v>
+        <v>7041473</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4577,7 +4582,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4588,11 +4593,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5387,42 +5387,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130011038</v>
+        <v>130011949</v>
       </c>
       <c r="B44" t="n">
-        <v>98735</v>
+        <v>57738</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220093</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506139</v>
+        <v>506072</v>
       </c>
       <c r="R44" t="n">
-        <v>7041442</v>
+        <v>7041512</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>1 vinterståndare i äldre granskog.</t>
+          <t>Färska födosöksspår/hackspår.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5479,7 +5479,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5503,10 +5502,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130011045</v>
+        <v>130011040</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>91659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5514,34 +5513,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506325</v>
+        <v>506158</v>
       </c>
       <c r="R45" t="n">
-        <v>7041726</v>
+        <v>7041729</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5578,7 +5580,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Växer i en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5587,8 +5589,34 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5605,7 +5633,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130011062</v>
+        <v>130011045</v>
       </c>
       <c r="B46" t="n">
         <v>79095</v>
@@ -5640,10 +5668,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>505881</v>
+        <v>506325</v>
       </c>
       <c r="R46" t="n">
-        <v>7041488</v>
+        <v>7041726</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5680,7 +5708,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5707,7 +5735,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130011056</v>
+        <v>130011062</v>
       </c>
       <c r="B47" t="n">
         <v>79095</v>
@@ -5742,10 +5770,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506125</v>
+        <v>505881</v>
       </c>
       <c r="R47" t="n">
-        <v>7041395</v>
+        <v>7041488</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5782,7 +5810,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5809,10 +5837,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130011949</v>
+        <v>130011056</v>
       </c>
       <c r="B48" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5820,42 +5848,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506072</v>
+        <v>506125</v>
       </c>
       <c r="R48" t="n">
-        <v>7041512</v>
+        <v>7041395</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5892,7 +5912,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska födosöksspår/hackspår.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5903,11 +5923,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5924,37 +5939,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130011040</v>
+        <v>130011038</v>
       </c>
       <c r="B49" t="n">
-        <v>91659</v>
+        <v>98735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>220093</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5962,10 +5982,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506158</v>
+        <v>506139</v>
       </c>
       <c r="R49" t="n">
-        <v>7041729</v>
+        <v>7041442</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6002,7 +6022,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Växer i en tvåstammig gran.</t>
+          <t>1 vinterståndare i äldre granskog.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6018,26 +6038,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130011025</v>
+        <v>130011054</v>
       </c>
       <c r="B55" t="n">
-        <v>57900</v>
+        <v>79095</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6654,50 +6654,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506100</v>
+        <v>506132</v>
       </c>
       <c r="R55" t="n">
-        <v>7041452</v>
+        <v>7041423</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6734,7 +6718,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 2 talltitor med lockläte I äldre luckig granskog.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6745,11 +6729,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6766,49 +6745,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130011029</v>
+        <v>130011053</v>
       </c>
       <c r="B56" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506106</v>
+        <v>506141</v>
       </c>
       <c r="R56" t="n">
-        <v>7041408</v>
+        <v>7041449</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6845,7 +6820,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt i granskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6854,14 +6829,8 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6878,7 +6847,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130011054</v>
+        <v>130011068</v>
       </c>
       <c r="B57" t="n">
         <v>79095</v>
@@ -6913,10 +6882,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506132</v>
+        <v>505745</v>
       </c>
       <c r="R57" t="n">
-        <v>7041423</v>
+        <v>7041395</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6953,7 +6922,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6980,10 +6949,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130011053</v>
+        <v>130011033</v>
       </c>
       <c r="B58" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6991,34 +6960,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506141</v>
+        <v>506221</v>
       </c>
       <c r="R58" t="n">
-        <v>7041449</v>
+        <v>7041401</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7055,7 +7027,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7064,8 +7036,34 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7082,10 +7080,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130011068</v>
+        <v>130011937</v>
       </c>
       <c r="B59" t="n">
-        <v>79095</v>
+        <v>91639</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7093,34 +7091,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>505745</v>
+        <v>506419</v>
       </c>
       <c r="R59" t="n">
-        <v>7041395</v>
+        <v>7041521</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7155,19 +7160,35 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7184,10 +7205,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130011033</v>
+        <v>130011025</v>
       </c>
       <c r="B60" t="n">
-        <v>80200</v>
+        <v>57900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7195,37 +7216,50 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506221</v>
+        <v>506100</v>
       </c>
       <c r="R60" t="n">
-        <v>7041401</v>
+        <v>7041452</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7262,7 +7296,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Minst 2 talltitor med lockläte I äldre luckig granskog.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7271,33 +7305,12 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7315,41 +7328,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130011937</v>
+        <v>130011029</v>
       </c>
       <c r="B61" t="n">
-        <v>91639</v>
+        <v>97702</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7357,10 +7367,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506419</v>
+        <v>506106</v>
       </c>
       <c r="R61" t="n">
-        <v>7041521</v>
+        <v>7041408</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7395,6 +7405,11 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt i granskog.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7408,21 +7423,6 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -10298,10 +10298,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130011946</v>
+        <v>130011061</v>
       </c>
       <c r="B86" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10309,42 +10309,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506026</v>
+        <v>505949</v>
       </c>
       <c r="R86" t="n">
-        <v>7041657</v>
+        <v>7041499</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10381,7 +10373,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10392,11 +10384,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10413,10 +10400,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130011061</v>
+        <v>130011946</v>
       </c>
       <c r="B87" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10424,34 +10411,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>505949</v>
+        <v>506026</v>
       </c>
       <c r="R87" t="n">
-        <v>7041499</v>
+        <v>7041657</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10488,7 +10483,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10499,6 +10494,11 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11351,41 +11351,37 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130022320</v>
+        <v>130022345</v>
       </c>
       <c r="B95" t="n">
-        <v>80229</v>
+        <v>82939</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11393,10 +11389,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>505800</v>
+        <v>506067</v>
       </c>
       <c r="R95" t="n">
-        <v>7041447</v>
+        <v>7041537</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11444,6 +11440,21 @@
       <c r="AH95" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11461,10 +11472,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130022345</v>
+        <v>130022295</v>
       </c>
       <c r="B96" t="n">
-        <v>82939</v>
+        <v>57741</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11472,26 +11483,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -11499,10 +11515,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>506067</v>
+        <v>506053</v>
       </c>
       <c r="R96" t="n">
-        <v>7041537</v>
+        <v>7041509</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11537,34 +11553,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11582,7 +11587,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130022295</v>
+        <v>130022304</v>
       </c>
       <c r="B97" t="n">
         <v>57741</v>
@@ -11625,10 +11630,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>506053</v>
+        <v>505975</v>
       </c>
       <c r="R97" t="n">
-        <v>7041509</v>
+        <v>7041661</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11697,40 +11702,39 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130022304</v>
+        <v>130022320</v>
       </c>
       <c r="B98" t="n">
-        <v>57741</v>
+        <v>80229</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -11740,10 +11744,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>505975</v>
+        <v>505800</v>
       </c>
       <c r="R98" t="n">
-        <v>7041661</v>
+        <v>7041447</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11778,17 +11782,13 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11812,10 +11812,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130022323</v>
+        <v>130022287</v>
       </c>
       <c r="B99" t="n">
-        <v>57738</v>
+        <v>57741</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11823,16 +11823,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -11843,7 +11843,11 @@
       <c r="I99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -11851,10 +11855,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>505858</v>
+        <v>506323</v>
       </c>
       <c r="R99" t="n">
-        <v>7041579</v>
+        <v>7041761</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11891,7 +11895,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Hackspår (födosöksspår).</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11923,10 +11927,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130022287</v>
+        <v>130022323</v>
       </c>
       <c r="B100" t="n">
-        <v>57741</v>
+        <v>57738</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11934,16 +11938,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11954,11 +11958,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11966,10 +11966,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>506323</v>
+        <v>505858</v>
       </c>
       <c r="R100" t="n">
-        <v>7041761</v>
+        <v>7041579</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Hackspår (födosöksspår).</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12159,40 +12159,39 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130022289</v>
+        <v>130022276</v>
       </c>
       <c r="B102" t="n">
-        <v>57741</v>
+        <v>91603</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -12202,10 +12201,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>506341</v>
+        <v>505821</v>
       </c>
       <c r="R102" t="n">
-        <v>7041723</v>
+        <v>7041557</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12240,17 +12239,13 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -12274,7 +12269,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130022294</v>
+        <v>130022289</v>
       </c>
       <c r="B103" t="n">
         <v>57741</v>
@@ -12317,10 +12312,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>506049</v>
+        <v>506341</v>
       </c>
       <c r="R103" t="n">
-        <v>7041511</v>
+        <v>7041723</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12389,10 +12384,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130011069</v>
+        <v>130022294</v>
       </c>
       <c r="B104" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12400,26 +12395,31 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12427,10 +12427,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>505714</v>
+        <v>506049</v>
       </c>
       <c r="R104" t="n">
-        <v>7041397</v>
+        <v>7041511</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12476,28 +12476,12 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -12515,39 +12499,40 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130022276</v>
+        <v>130022290</v>
       </c>
       <c r="B105" t="n">
-        <v>91603</v>
+        <v>57741</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -12557,10 +12542,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>505821</v>
+        <v>506432</v>
       </c>
       <c r="R105" t="n">
-        <v>7041557</v>
+        <v>7041517</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12595,13 +12580,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -12625,10 +12614,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130022290</v>
+        <v>130011069</v>
       </c>
       <c r="B106" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12636,31 +12625,26 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -12668,10 +12652,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506432</v>
+        <v>505714</v>
       </c>
       <c r="R106" t="n">
-        <v>7041517</v>
+        <v>7041397</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12708,7 +12692,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12717,12 +12701,28 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14887,10 +14887,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130022300</v>
+        <v>130022267</v>
       </c>
       <c r="B125" t="n">
-        <v>57741</v>
+        <v>83073</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14898,31 +14898,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -14930,10 +14925,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>506005</v>
+        <v>506213</v>
       </c>
       <c r="R125" t="n">
-        <v>7041651</v>
+        <v>7041527</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14968,23 +14963,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -15002,10 +15008,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130022306</v>
+        <v>130022272</v>
       </c>
       <c r="B126" t="n">
-        <v>57741</v>
+        <v>83073</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15013,31 +15019,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -15045,10 +15046,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>505833</v>
+        <v>505861</v>
       </c>
       <c r="R126" t="n">
-        <v>7041571</v>
+        <v>7041553</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15083,23 +15084,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -15117,10 +15129,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130022333</v>
+        <v>130022300</v>
       </c>
       <c r="B127" t="n">
-        <v>91635</v>
+        <v>57741</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15128,28 +15140,29 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -15159,10 +15172,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>506291</v>
+        <v>506005</v>
       </c>
       <c r="R127" t="n">
-        <v>7041817</v>
+        <v>7041651</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15197,34 +15210,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -15242,10 +15244,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130022267</v>
+        <v>130022349</v>
       </c>
       <c r="B128" t="n">
-        <v>83073</v>
+        <v>83065</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15253,21 +15255,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15280,10 +15282,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>506213</v>
+        <v>505803</v>
       </c>
       <c r="R128" t="n">
-        <v>7041527</v>
+        <v>7041538</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15331,21 +15333,6 @@
       <c r="AH128" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -15363,10 +15350,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130022272</v>
+        <v>130022333</v>
       </c>
       <c r="B129" t="n">
-        <v>83073</v>
+        <v>91635</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15374,26 +15361,30 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -15401,10 +15392,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>505861</v>
+        <v>506291</v>
       </c>
       <c r="R129" t="n">
-        <v>7041553</v>
+        <v>7041817</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15484,10 +15475,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130022349</v>
+        <v>130022336</v>
       </c>
       <c r="B130" t="n">
-        <v>83065</v>
+        <v>91635</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15495,26 +15486,30 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -15522,10 +15517,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>505803</v>
+        <v>505807</v>
       </c>
       <c r="R130" t="n">
-        <v>7041538</v>
+        <v>7041535</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15573,6 +15568,21 @@
       <c r="AH130" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -15590,10 +15600,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130022336</v>
+        <v>130022306</v>
       </c>
       <c r="B131" t="n">
-        <v>91635</v>
+        <v>57741</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15601,28 +15611,29 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -15632,10 +15643,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>505807</v>
+        <v>505833</v>
       </c>
       <c r="R131" t="n">
-        <v>7041535</v>
+        <v>7041571</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15670,34 +15681,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15715,32 +15715,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130022280</v>
+        <v>130022282</v>
       </c>
       <c r="B132" t="n">
-        <v>91639</v>
+        <v>92357</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15757,10 +15757,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>505798</v>
+        <v>505786</v>
       </c>
       <c r="R132" t="n">
-        <v>7041503</v>
+        <v>7041510</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15808,26 +15808,6 @@
       <c r="AH132" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15845,39 +15825,40 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130022282</v>
+        <v>130022293</v>
       </c>
       <c r="B133" t="n">
-        <v>92357</v>
+        <v>57741</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -15887,10 +15868,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>505786</v>
+        <v>506204</v>
       </c>
       <c r="R133" t="n">
-        <v>7041510</v>
+        <v>7041525</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15925,13 +15906,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -15955,7 +15940,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130022293</v>
+        <v>130022283</v>
       </c>
       <c r="B134" t="n">
         <v>57741</v>
@@ -15998,10 +15983,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>506204</v>
+        <v>506152</v>
       </c>
       <c r="R134" t="n">
-        <v>7041525</v>
+        <v>7041714</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16070,10 +16055,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130022283</v>
+        <v>130022317</v>
       </c>
       <c r="B135" t="n">
-        <v>57741</v>
+        <v>57900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16081,42 +16066,50 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>506152</v>
+        <v>505940</v>
       </c>
       <c r="R135" t="n">
-        <v>7041714</v>
+        <v>7041639</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16151,11 +16144,6 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -16168,6 +16156,11 @@
       <c r="AH135" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>Flerskiktad skog i många delar.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -16185,10 +16178,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130022317</v>
+        <v>130022280</v>
       </c>
       <c r="B136" t="n">
-        <v>57900</v>
+        <v>91639</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16196,50 +16189,41 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>505940</v>
+        <v>505798</v>
       </c>
       <c r="R136" t="n">
-        <v>7041639</v>
+        <v>7041503</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16280,6 +16264,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -16288,9 +16273,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>Flerskiktad skog i många delar.</t>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130022341</v>
+        <v>130022348</v>
       </c>
       <c r="B147" t="n">
-        <v>91659</v>
+        <v>83065</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17485,26 +17485,26 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr"/>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
@@ -17512,10 +17512,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>505857</v>
+        <v>505781</v>
       </c>
       <c r="R147" t="n">
-        <v>7041565</v>
+        <v>7041499</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17563,21 +17563,6 @@
       <c r="AH147" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -17595,10 +17580,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130022332</v>
+        <v>130022341</v>
       </c>
       <c r="B148" t="n">
-        <v>56922</v>
+        <v>91659</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17606,50 +17591,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>505757</v>
+        <v>505857</v>
       </c>
       <c r="R148" t="n">
-        <v>7041488</v>
+        <v>7041565</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17690,12 +17662,28 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -17713,10 +17701,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130022348</v>
+        <v>130022332</v>
       </c>
       <c r="B149" t="n">
-        <v>83065</v>
+        <v>56922</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17724,37 +17712,50 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>308</v>
+        <v>102612</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>505781</v>
+        <v>505757</v>
       </c>
       <c r="R149" t="n">
-        <v>7041499</v>
+        <v>7041488</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17795,7 +17796,6 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55492-2025 artfynd.xlsx
+++ b/artfynd/A 55492-2025 artfynd.xlsx
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129921258</v>
+        <v>129921246</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,34 +1024,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506384</v>
+        <v>505962</v>
       </c>
       <c r="R5" t="n">
-        <v>7041622</v>
+        <v>7041505</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1096,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129921257</v>
+        <v>129921258</v>
       </c>
       <c r="B6" t="n">
         <v>79095</v>
@@ -1150,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506139</v>
+        <v>506384</v>
       </c>
       <c r="R6" t="n">
-        <v>7041701</v>
+        <v>7041622</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129921246</v>
+        <v>129921257</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1228,42 +1236,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505962</v>
+        <v>506139</v>
       </c>
       <c r="R7" t="n">
-        <v>7041505</v>
+        <v>7041701</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,7 +1330,7 @@
         <v>129921255</v>
       </c>
       <c r="B8" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129921266</v>
+        <v>129921259</v>
       </c>
       <c r="B11" t="n">
         <v>79095</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505882</v>
+        <v>506192</v>
       </c>
       <c r="R11" t="n">
-        <v>7041492</v>
+        <v>7041434</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På välhackad död gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129921259</v>
+        <v>129921266</v>
       </c>
       <c r="B12" t="n">
         <v>79095</v>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506192</v>
+        <v>505882</v>
       </c>
       <c r="R12" t="n">
-        <v>7041434</v>
+        <v>7041492</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På välhackad död gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2602,10 +2602,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129921251</v>
+        <v>129921261</v>
       </c>
       <c r="B20" t="n">
-        <v>80201</v>
+        <v>79095</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,37 +2613,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506126</v>
+        <v>506155</v>
       </c>
       <c r="R20" t="n">
-        <v>7041425</v>
+        <v>7041475</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,7 +2677,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt, på sälg</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2689,24 +2686,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>vanlig sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea subsp. caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea subsp. caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2723,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129921261</v>
+        <v>129921251</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>80201</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,34 +2715,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506155</v>
+        <v>506126</v>
       </c>
       <c r="R21" t="n">
-        <v>7041475</v>
+        <v>7041425</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,7 +2782,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Rikligt, på sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2807,8 +2791,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>vanlig sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2825,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130011057</v>
+        <v>130011026</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,28 +2836,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2867,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506098</v>
+        <v>506225</v>
       </c>
       <c r="R22" t="n">
-        <v>7041446</v>
+        <v>7041468</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2908,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt med bålar och med apothecier.</t>
+          <t>Äldre rejäla hackspår i en levande stående gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2916,7 +2917,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130011026</v>
+        <v>130011057</v>
       </c>
       <c r="B23" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2971,29 +2971,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3003,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506225</v>
+        <v>506098</v>
       </c>
       <c r="R23" t="n">
-        <v>7041468</v>
+        <v>7041446</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,7 +3042,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre rejäla hackspår i en levande stående gran.</t>
+          <t>Rikligt med bålar och med apothecier.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,6 +3051,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3072,12 +3072,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3095,45 +3095,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130011960</v>
+        <v>130011936</v>
       </c>
       <c r="B24" t="n">
-        <v>82939</v>
+        <v>91605</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505875</v>
+        <v>506219</v>
       </c>
       <c r="R24" t="n">
-        <v>7041542</v>
+        <v>7041490</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3181,21 +3188,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3213,7 +3205,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130011943</v>
+        <v>130011022</v>
       </c>
       <c r="B25" t="n">
         <v>57741</v>
@@ -3246,7 +3238,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506047</v>
+        <v>506105</v>
       </c>
       <c r="R25" t="n">
-        <v>7041498</v>
+        <v>7041429</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3296,7 +3288,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3311,6 +3303,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3443,7 +3455,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130011022</v>
+        <v>130011943</v>
       </c>
       <c r="B27" t="n">
         <v>57741</v>
@@ -3476,7 +3488,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3486,10 +3498,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506105</v>
+        <v>506047</v>
       </c>
       <c r="R27" t="n">
-        <v>7041429</v>
+        <v>7041498</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,7 +3538,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,26 +3553,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3578,52 +3570,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130011936</v>
+        <v>130011960</v>
       </c>
       <c r="B28" t="n">
-        <v>91603</v>
+        <v>82939</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506219</v>
+        <v>505875</v>
       </c>
       <c r="R28" t="n">
-        <v>7041490</v>
+        <v>7041542</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3671,6 +3656,21 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130011027</v>
+        <v>130011959</v>
       </c>
       <c r="B30" t="n">
-        <v>57738</v>
+        <v>82939</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3814,42 +3814,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505811</v>
+        <v>505869</v>
       </c>
       <c r="R30" t="n">
-        <v>7041517</v>
+        <v>7041576</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3884,17 +3876,13 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rejäla äldre hackspår i en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3913,14 +3901,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3938,10 +3921,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130011959</v>
+        <v>130011051</v>
       </c>
       <c r="B31" t="n">
-        <v>82939</v>
+        <v>79095</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3949,21 +3932,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3973,10 +3956,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505869</v>
+        <v>506173</v>
       </c>
       <c r="R31" t="n">
-        <v>7041576</v>
+        <v>7041436</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4011,35 +3994,19 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På flera granar i granskog.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4056,10 +4023,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130011051</v>
+        <v>130011027</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,34 +4034,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506173</v>
+        <v>505811</v>
       </c>
       <c r="R32" t="n">
-        <v>7041436</v>
+        <v>7041517</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4131,7 +4106,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>Rejäla äldre hackspår i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4142,6 +4117,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4273,61 +4273,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130011036</v>
+        <v>130011955</v>
       </c>
       <c r="B34" t="n">
-        <v>57845</v>
+        <v>79095</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>505812</v>
+        <v>506094</v>
       </c>
       <c r="R34" t="n">
-        <v>7041524</v>
+        <v>7041562</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4364,7 +4351,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>2 nyfikna lavskrikor med lockläte i flerskiktad granskog med bitvis rikligt med garnlav på gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4373,6 +4360,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4396,7 +4384,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130011955</v>
+        <v>130011058</v>
       </c>
       <c r="B35" t="n">
         <v>79095</v>
@@ -4425,19 +4413,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506094</v>
+        <v>506127</v>
       </c>
       <c r="R35" t="n">
-        <v>7041562</v>
+        <v>7041473</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4474,7 +4459,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4483,14 +4468,8 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4507,45 +4486,61 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130011058</v>
+        <v>130011036</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>57845</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506127</v>
+        <v>505812</v>
       </c>
       <c r="R36" t="n">
-        <v>7041473</v>
+        <v>7041524</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4582,7 +4577,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>2 nyfikna lavskrikor med lockläte i flerskiktad granskog med bitvis rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4593,6 +4588,11 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4742,7 +4742,7 @@
         <v>130011939</v>
       </c>
       <c r="B38" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130011944</v>
+        <v>130011049</v>
       </c>
       <c r="B39" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4875,42 +4875,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506053</v>
+        <v>506235</v>
       </c>
       <c r="R39" t="n">
-        <v>7041506</v>
+        <v>7041415</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4947,7 +4939,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4958,11 +4950,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4979,10 +4966,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130011049</v>
+        <v>130011944</v>
       </c>
       <c r="B40" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4990,34 +4977,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506235</v>
+        <v>506053</v>
       </c>
       <c r="R40" t="n">
-        <v>7041415</v>
+        <v>7041506</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5054,7 +5049,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5065,6 +5060,11 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5502,10 +5502,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130011040</v>
+        <v>130011045</v>
       </c>
       <c r="B45" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5513,37 +5513,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506158</v>
+        <v>506325</v>
       </c>
       <c r="R45" t="n">
-        <v>7041729</v>
+        <v>7041726</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5580,7 +5577,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Växer i en tvåstammig gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5589,34 +5586,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5633,7 +5604,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130011045</v>
+        <v>130011062</v>
       </c>
       <c r="B46" t="n">
         <v>79095</v>
@@ -5668,10 +5639,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506325</v>
+        <v>505881</v>
       </c>
       <c r="R46" t="n">
-        <v>7041726</v>
+        <v>7041488</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5708,7 +5679,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5735,7 +5706,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130011062</v>
+        <v>130011056</v>
       </c>
       <c r="B47" t="n">
         <v>79095</v>
@@ -5770,10 +5741,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505881</v>
+        <v>506125</v>
       </c>
       <c r="R47" t="n">
-        <v>7041488</v>
+        <v>7041395</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5810,7 +5781,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5837,10 +5808,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130011056</v>
+        <v>130011040</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>91661</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5848,34 +5819,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506125</v>
+        <v>506158</v>
       </c>
       <c r="R48" t="n">
-        <v>7041395</v>
+        <v>7041729</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5912,7 +5886,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Växer i en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5921,8 +5895,34 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5942,7 +5942,7 @@
         <v>130011038</v>
       </c>
       <c r="B49" t="n">
-        <v>98735</v>
+        <v>98737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6055,10 +6055,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130011063</v>
+        <v>130011028</v>
       </c>
       <c r="B50" t="n">
-        <v>79095</v>
+        <v>80201</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6066,34 +6066,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505931</v>
+        <v>506225</v>
       </c>
       <c r="R50" t="n">
-        <v>7041478</v>
+        <v>7041457</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6130,7 +6133,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en smal rönn.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6139,8 +6142,34 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6157,52 +6186,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130011035</v>
+        <v>130011063</v>
       </c>
       <c r="B51" t="n">
-        <v>80236</v>
+        <v>79095</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506220</v>
+        <v>505931</v>
       </c>
       <c r="R51" t="n">
-        <v>7041401</v>
+        <v>7041478</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6239,7 +6261,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6248,34 +6270,8 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6292,10 +6288,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130011028</v>
+        <v>130011052</v>
       </c>
       <c r="B52" t="n">
-        <v>80201</v>
+        <v>79095</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6303,34 +6299,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506225</v>
+        <v>506151</v>
       </c>
       <c r="R52" t="n">
         <v>7041457</v>
@@ -6370,7 +6363,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På en smal rönn.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6379,34 +6372,8 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6541,45 +6508,52 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130011052</v>
+        <v>130011035</v>
       </c>
       <c r="B54" t="n">
-        <v>79095</v>
+        <v>80236</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506151</v>
+        <v>506220</v>
       </c>
       <c r="R54" t="n">
-        <v>7041457</v>
+        <v>7041401</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6616,7 +6590,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6625,8 +6599,34 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6643,10 +6643,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130011054</v>
+        <v>130011033</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6654,34 +6654,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506132</v>
+        <v>506221</v>
       </c>
       <c r="R55" t="n">
-        <v>7041423</v>
+        <v>7041401</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6718,7 +6721,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6727,8 +6730,34 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6745,7 +6774,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130011053</v>
+        <v>130011068</v>
       </c>
       <c r="B56" t="n">
         <v>79095</v>
@@ -6780,10 +6809,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506141</v>
+        <v>505745</v>
       </c>
       <c r="R56" t="n">
-        <v>7041449</v>
+        <v>7041395</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6820,7 +6849,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6847,10 +6876,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130011068</v>
+        <v>130011937</v>
       </c>
       <c r="B57" t="n">
-        <v>79095</v>
+        <v>91641</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6858,34 +6887,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>505745</v>
+        <v>506419</v>
       </c>
       <c r="R57" t="n">
-        <v>7041395</v>
+        <v>7041521</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6920,19 +6956,35 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -6949,10 +7001,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130011033</v>
+        <v>130011025</v>
       </c>
       <c r="B58" t="n">
-        <v>80200</v>
+        <v>57900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6960,37 +7012,50 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506221</v>
+        <v>506100</v>
       </c>
       <c r="R58" t="n">
-        <v>7041401</v>
+        <v>7041452</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7027,7 +7092,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Minst 2 talltitor med lockläte I äldre luckig granskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7036,33 +7101,12 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7080,10 +7124,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130011937</v>
+        <v>130011054</v>
       </c>
       <c r="B59" t="n">
-        <v>91639</v>
+        <v>79095</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7091,41 +7135,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506419</v>
+        <v>506132</v>
       </c>
       <c r="R59" t="n">
-        <v>7041521</v>
+        <v>7041423</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7160,35 +7197,19 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7205,10 +7226,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130011025</v>
+        <v>130011053</v>
       </c>
       <c r="B60" t="n">
-        <v>57900</v>
+        <v>79095</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7216,50 +7237,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506100</v>
+        <v>506141</v>
       </c>
       <c r="R60" t="n">
-        <v>7041452</v>
+        <v>7041449</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7296,7 +7301,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Minst 2 talltitor med lockläte I äldre luckig granskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7307,11 +7312,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7331,7 +7331,7 @@
         <v>130011029</v>
       </c>
       <c r="B61" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7561,10 +7561,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130011954</v>
+        <v>130011938</v>
       </c>
       <c r="B63" t="n">
-        <v>79095</v>
+        <v>91641</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7572,26 +7572,30 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7599,10 +7603,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506077</v>
+        <v>506088</v>
       </c>
       <c r="R63" t="n">
-        <v>7041514</v>
+        <v>7041532</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7637,11 +7641,6 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Riklig förekomst med gott om garnlavsbålar.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7655,6 +7654,21 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7803,10 +7817,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130011938</v>
+        <v>130011954</v>
       </c>
       <c r="B65" t="n">
-        <v>91639</v>
+        <v>79095</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7814,30 +7828,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7845,10 +7855,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506088</v>
+        <v>506077</v>
       </c>
       <c r="R65" t="n">
-        <v>7041532</v>
+        <v>7041514</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7883,6 +7893,11 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Riklig förekomst med gott om garnlavsbålar.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7896,21 +7911,6 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7928,10 +7928,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130011041</v>
+        <v>130011021</v>
       </c>
       <c r="B66" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7939,24 +7939,29 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7966,10 +7971,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506282</v>
+        <v>506131</v>
       </c>
       <c r="R66" t="n">
-        <v>7041798</v>
+        <v>7041380</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8006,7 +8011,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående gran med 33 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8015,7 +8020,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8059,10 +8063,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130011050</v>
+        <v>130011020</v>
       </c>
       <c r="B67" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8070,26 +8074,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8097,10 +8106,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506188</v>
+        <v>506133</v>
       </c>
       <c r="R67" t="n">
-        <v>7041400</v>
+        <v>7041369</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8137,7 +8146,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På bark och gren av björk i äldre granskog.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8146,7 +8155,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8157,22 +8165,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8190,10 +8198,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130011046</v>
+        <v>130011041</v>
       </c>
       <c r="B68" t="n">
-        <v>79095</v>
+        <v>91661</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8201,34 +8209,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506348</v>
+        <v>506282</v>
       </c>
       <c r="R68" t="n">
-        <v>7041704</v>
+        <v>7041798</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8265,7 +8276,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Flera fruktkroppar i en stående gran med 33 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8274,8 +8285,34 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8292,10 +8329,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130011021</v>
+        <v>130011050</v>
       </c>
       <c r="B69" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8303,31 +8340,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8335,10 +8367,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506131</v>
+        <v>506188</v>
       </c>
       <c r="R69" t="n">
-        <v>7041380</v>
+        <v>7041400</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8375,7 +8407,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran i äldre granskog.</t>
+          <t>På bark och gren av björk i äldre granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8384,6 +8416,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8394,22 +8427,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8427,10 +8460,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130011020</v>
+        <v>130011046</v>
       </c>
       <c r="B70" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8438,42 +8471,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506133</v>
+        <v>506348</v>
       </c>
       <c r="R70" t="n">
-        <v>7041369</v>
+        <v>7041704</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8510,7 +8535,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8521,31 +8546,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8908,7 +8908,7 @@
         <v>130011039</v>
       </c>
       <c r="B74" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9040,10 +9040,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130011019</v>
+        <v>130011055</v>
       </c>
       <c r="B75" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9051,42 +9051,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506192</v>
+        <v>506137</v>
       </c>
       <c r="R75" t="n">
-        <v>7041460</v>
+        <v>7041384</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9123,7 +9115,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 5 meter på en granstam.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9134,31 +9126,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9175,10 +9142,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130011942</v>
+        <v>130011070</v>
       </c>
       <c r="B76" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9186,42 +9153,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506378</v>
+        <v>505697</v>
       </c>
       <c r="R76" t="n">
-        <v>7041569</v>
+        <v>7041399</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9258,7 +9217,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9269,11 +9228,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9290,7 +9244,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130011055</v>
+        <v>130011043</v>
       </c>
       <c r="B77" t="n">
         <v>79095</v>
@@ -9325,10 +9279,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506137</v>
+        <v>506144</v>
       </c>
       <c r="R77" t="n">
-        <v>7041384</v>
+        <v>7041702</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9392,10 +9346,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130011070</v>
+        <v>130011942</v>
       </c>
       <c r="B78" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9403,34 +9357,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>505697</v>
+        <v>506378</v>
       </c>
       <c r="R78" t="n">
-        <v>7041399</v>
+        <v>7041569</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9467,7 +9429,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9478,6 +9440,11 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9494,10 +9461,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130011043</v>
+        <v>130011019</v>
       </c>
       <c r="B79" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9505,34 +9472,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506144</v>
+        <v>506192</v>
       </c>
       <c r="R79" t="n">
-        <v>7041702</v>
+        <v>7041460</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9569,7 +9544,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, längs minst 5 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9580,6 +9555,31 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9596,10 +9596,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130011065</v>
+        <v>130011953</v>
       </c>
       <c r="B80" t="n">
-        <v>79095</v>
+        <v>91661</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9607,34 +9607,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505816</v>
+        <v>506196</v>
       </c>
       <c r="R80" t="n">
-        <v>7041475</v>
+        <v>7041474</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9669,19 +9672,35 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9698,10 +9717,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130011956</v>
+        <v>130011042</v>
       </c>
       <c r="B81" t="n">
-        <v>79095</v>
+        <v>91661</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9709,26 +9728,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -9736,10 +9755,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505707</v>
+        <v>505757</v>
       </c>
       <c r="R81" t="n">
-        <v>7041435</v>
+        <v>7041406</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9776,7 +9795,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>I en klen granhögstubbe.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9792,6 +9811,26 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9809,7 +9848,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130011059</v>
+        <v>130011065</v>
       </c>
       <c r="B82" t="n">
         <v>79095</v>
@@ -9844,10 +9883,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506131</v>
+        <v>505816</v>
       </c>
       <c r="R82" t="n">
-        <v>7041516</v>
+        <v>7041475</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9911,10 +9950,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130011024</v>
+        <v>130011956</v>
       </c>
       <c r="B83" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9922,31 +9961,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9954,10 +9988,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>505908</v>
+        <v>505707</v>
       </c>
       <c r="R83" t="n">
-        <v>7041477</v>
+        <v>7041435</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9994,7 +10028,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran i gammal granskog.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10003,32 +10037,13 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10046,10 +10061,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130011953</v>
+        <v>130011059</v>
       </c>
       <c r="B84" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10057,37 +10072,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506196</v>
+        <v>506131</v>
       </c>
       <c r="R84" t="n">
-        <v>7041474</v>
+        <v>7041516</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10122,35 +10134,19 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10167,10 +10163,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130011042</v>
+        <v>130011024</v>
       </c>
       <c r="B85" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10178,24 +10174,29 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -10205,10 +10206,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>505757</v>
+        <v>505908</v>
       </c>
       <c r="R85" t="n">
-        <v>7041406</v>
+        <v>7041477</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10245,7 +10246,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>I en klen granhögstubbe.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10254,7 +10255,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10275,12 +10275,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10617,10 +10617,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130011032</v>
+        <v>130011945</v>
       </c>
       <c r="B89" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10628,28 +10628,29 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -10659,10 +10660,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>506224</v>
+        <v>506106</v>
       </c>
       <c r="R89" t="n">
-        <v>7041455</v>
+        <v>7041570</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10699,7 +10700,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På en smal rönn.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10708,33 +10709,12 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10752,10 +10732,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130011945</v>
+        <v>130011032</v>
       </c>
       <c r="B90" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10763,29 +10743,28 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -10795,10 +10774,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>506106</v>
+        <v>506224</v>
       </c>
       <c r="R90" t="n">
-        <v>7041570</v>
+        <v>7041455</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10835,7 +10814,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På en smal rönn.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10844,12 +10823,33 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10988,7 +10988,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130022271</v>
+        <v>130022274</v>
       </c>
       <c r="B92" t="n">
         <v>83073</v>
@@ -11026,10 +11026,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>505900</v>
+        <v>505805</v>
       </c>
       <c r="R92" t="n">
-        <v>7041531</v>
+        <v>7041535</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11109,7 +11109,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130022274</v>
+        <v>130022271</v>
       </c>
       <c r="B93" t="n">
         <v>83073</v>
@@ -11147,10 +11147,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>505805</v>
+        <v>505900</v>
       </c>
       <c r="R93" t="n">
-        <v>7041535</v>
+        <v>7041531</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11230,10 +11230,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130022273</v>
+        <v>130022345</v>
       </c>
       <c r="B94" t="n">
-        <v>83073</v>
+        <v>82939</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11241,21 +11241,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>505812</v>
+        <v>506067</v>
       </c>
       <c r="R94" t="n">
-        <v>7041524</v>
+        <v>7041537</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11351,37 +11351,41 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130022345</v>
+        <v>130022320</v>
       </c>
       <c r="B95" t="n">
-        <v>82939</v>
+        <v>80229</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11389,10 +11393,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>506067</v>
+        <v>505800</v>
       </c>
       <c r="R95" t="n">
-        <v>7041537</v>
+        <v>7041447</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11440,21 +11444,6 @@
       <c r="AH95" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11472,10 +11461,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130022295</v>
+        <v>130022273</v>
       </c>
       <c r="B96" t="n">
-        <v>57741</v>
+        <v>83073</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11483,31 +11472,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -11515,10 +11499,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>506053</v>
+        <v>505812</v>
       </c>
       <c r="R96" t="n">
-        <v>7041509</v>
+        <v>7041524</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11553,23 +11537,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11587,7 +11582,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130022304</v>
+        <v>130022295</v>
       </c>
       <c r="B97" t="n">
         <v>57741</v>
@@ -11630,10 +11625,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>505975</v>
+        <v>506053</v>
       </c>
       <c r="R97" t="n">
-        <v>7041661</v>
+        <v>7041509</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11702,39 +11697,40 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130022320</v>
+        <v>130022304</v>
       </c>
       <c r="B98" t="n">
-        <v>80229</v>
+        <v>57741</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -11744,10 +11740,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>505800</v>
+        <v>505975</v>
       </c>
       <c r="R98" t="n">
-        <v>7041447</v>
+        <v>7041661</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11782,13 +11778,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -12162,7 +12162,7 @@
         <v>130022276</v>
       </c>
       <c r="B102" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12269,10 +12269,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130022289</v>
+        <v>130011069</v>
       </c>
       <c r="B103" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12280,31 +12280,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12312,10 +12307,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>506341</v>
+        <v>505714</v>
       </c>
       <c r="R103" t="n">
-        <v>7041723</v>
+        <v>7041397</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12352,7 +12347,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12361,12 +12356,28 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12384,7 +12395,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130022294</v>
+        <v>130022289</v>
       </c>
       <c r="B104" t="n">
         <v>57741</v>
@@ -12427,10 +12438,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>506049</v>
+        <v>506341</v>
       </c>
       <c r="R104" t="n">
-        <v>7041511</v>
+        <v>7041723</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12614,10 +12625,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130011069</v>
+        <v>130022294</v>
       </c>
       <c r="B106" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12625,26 +12636,31 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -12652,10 +12668,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>505714</v>
+        <v>506049</v>
       </c>
       <c r="R106" t="n">
-        <v>7041397</v>
+        <v>7041511</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12692,7 +12708,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12701,28 +12717,12 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12740,10 +12740,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130022328</v>
+        <v>130022309</v>
       </c>
       <c r="B107" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12751,26 +12751,31 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -12778,10 +12783,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>505804</v>
+        <v>505816</v>
       </c>
       <c r="R107" t="n">
-        <v>7041453</v>
+        <v>7041559</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12816,13 +12821,17 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -12846,10 +12855,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130022309</v>
+        <v>130022328</v>
       </c>
       <c r="B108" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12857,31 +12866,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -12889,10 +12893,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>505816</v>
+        <v>505804</v>
       </c>
       <c r="R108" t="n">
-        <v>7041559</v>
+        <v>7041453</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12927,17 +12931,13 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -12961,10 +12961,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130022268</v>
+        <v>130022278</v>
       </c>
       <c r="B109" t="n">
-        <v>83073</v>
+        <v>91641</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12972,26 +12972,30 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -12999,10 +13003,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506167</v>
+        <v>506225</v>
       </c>
       <c r="R109" t="n">
-        <v>7041474</v>
+        <v>7041439</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13062,9 +13066,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -13082,10 +13091,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130022278</v>
+        <v>130022268</v>
       </c>
       <c r="B110" t="n">
-        <v>91639</v>
+        <v>83073</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13093,30 +13102,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -13124,10 +13129,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506225</v>
+        <v>506167</v>
       </c>
       <c r="R110" t="n">
-        <v>7041439</v>
+        <v>7041474</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13187,14 +13192,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -13327,7 +13327,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130022307</v>
+        <v>130022298</v>
       </c>
       <c r="B112" t="n">
         <v>57741</v>
@@ -13360,7 +13360,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -13370,10 +13370,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>505833</v>
+        <v>506051</v>
       </c>
       <c r="R112" t="n">
-        <v>7041575</v>
+        <v>7041538</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13410,7 +13410,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13442,7 +13442,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130022284</v>
+        <v>130022307</v>
       </c>
       <c r="B113" t="n">
         <v>57741</v>
@@ -13475,7 +13475,7 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -13485,10 +13485,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>506133</v>
+        <v>505833</v>
       </c>
       <c r="R113" t="n">
-        <v>7041711</v>
+        <v>7041575</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13525,7 +13525,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13557,7 +13557,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130022298</v>
+        <v>130022284</v>
       </c>
       <c r="B114" t="n">
         <v>57741</v>
@@ -13600,10 +13600,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>506051</v>
+        <v>506133</v>
       </c>
       <c r="R114" t="n">
-        <v>7041538</v>
+        <v>7041711</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13672,10 +13672,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130022305</v>
+        <v>130022279</v>
       </c>
       <c r="B115" t="n">
-        <v>57741</v>
+        <v>91641</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13683,29 +13683,28 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -13715,10 +13714,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>505839</v>
+        <v>505790</v>
       </c>
       <c r="R115" t="n">
-        <v>7041578</v>
+        <v>7041489</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13753,23 +13752,39 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -13787,10 +13802,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130022301</v>
+        <v>130022335</v>
       </c>
       <c r="B116" t="n">
-        <v>57741</v>
+        <v>91637</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13798,29 +13813,28 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -13830,10 +13844,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>506003</v>
+        <v>506111</v>
       </c>
       <c r="R116" t="n">
-        <v>7041648</v>
+        <v>7041602</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13868,23 +13882,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13902,10 +13927,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130022308</v>
+        <v>130022330</v>
       </c>
       <c r="B117" t="n">
-        <v>57741</v>
+        <v>78107</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13913,31 +13938,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13945,10 +13965,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>505820</v>
+        <v>505898</v>
       </c>
       <c r="R117" t="n">
-        <v>7041561</v>
+        <v>7041518</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13983,23 +14003,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14017,10 +14048,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130022314</v>
+        <v>130022340</v>
       </c>
       <c r="B118" t="n">
-        <v>57741</v>
+        <v>91661</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14028,54 +14059,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>505807</v>
+        <v>506102</v>
       </c>
       <c r="R118" t="n">
-        <v>7041547</v>
+        <v>7041588</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14110,23 +14124,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Födosökande hane i en yta med mycket höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved främst av gran.</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14144,10 +14169,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130022330</v>
+        <v>130022322</v>
       </c>
       <c r="B119" t="n">
-        <v>78107</v>
+        <v>91592</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14155,26 +14180,30 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228579</v>
+        <v>112</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -14182,10 +14211,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>505898</v>
+        <v>506082</v>
       </c>
       <c r="R119" t="n">
-        <v>7041518</v>
+        <v>7041551</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14265,10 +14294,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130022322</v>
+        <v>130022314</v>
       </c>
       <c r="B120" t="n">
-        <v>91590</v>
+        <v>57741</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14276,41 +14305,54 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>506082</v>
+        <v>505807</v>
       </c>
       <c r="R120" t="n">
-        <v>7041551</v>
+        <v>7041547</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14345,34 +14387,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Födosökande hane i en yta med mycket höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved främst av gran.</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14390,10 +14421,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130022279</v>
+        <v>130022308</v>
       </c>
       <c r="B121" t="n">
-        <v>91639</v>
+        <v>57741</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14401,28 +14432,29 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -14432,10 +14464,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>505790</v>
+        <v>505820</v>
       </c>
       <c r="R121" t="n">
-        <v>7041489</v>
+        <v>7041561</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14470,39 +14502,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14520,10 +14536,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130022335</v>
+        <v>130022301</v>
       </c>
       <c r="B122" t="n">
-        <v>91635</v>
+        <v>57741</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14531,28 +14547,29 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -14562,10 +14579,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>506111</v>
+        <v>506003</v>
       </c>
       <c r="R122" t="n">
-        <v>7041602</v>
+        <v>7041648</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14600,34 +14617,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14645,10 +14651,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130022340</v>
+        <v>130022305</v>
       </c>
       <c r="B123" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14656,24 +14662,29 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -14683,10 +14694,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>506102</v>
+        <v>505839</v>
       </c>
       <c r="R123" t="n">
-        <v>7041588</v>
+        <v>7041578</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14721,34 +14732,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -14766,7 +14766,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130022265</v>
+        <v>130022272</v>
       </c>
       <c r="B124" t="n">
         <v>83073</v>
@@ -14804,10 +14804,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>506287</v>
+        <v>505861</v>
       </c>
       <c r="R124" t="n">
-        <v>7041437</v>
+        <v>7041553</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15008,10 +15008,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130022272</v>
+        <v>130022349</v>
       </c>
       <c r="B126" t="n">
-        <v>83073</v>
+        <v>83065</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15019,21 +15019,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -15046,10 +15046,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>505861</v>
+        <v>505803</v>
       </c>
       <c r="R126" t="n">
-        <v>7041553</v>
+        <v>7041538</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15097,21 +15097,6 @@
       <c r="AH126" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -15129,10 +15114,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130022300</v>
+        <v>130022333</v>
       </c>
       <c r="B127" t="n">
-        <v>57741</v>
+        <v>91637</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15140,29 +15125,28 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -15172,10 +15156,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>506005</v>
+        <v>506291</v>
       </c>
       <c r="R127" t="n">
-        <v>7041651</v>
+        <v>7041817</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15210,23 +15194,34 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -15244,10 +15239,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130022349</v>
+        <v>130022336</v>
       </c>
       <c r="B128" t="n">
-        <v>83065</v>
+        <v>91637</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15255,26 +15250,30 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -15282,10 +15281,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>505803</v>
+        <v>505807</v>
       </c>
       <c r="R128" t="n">
-        <v>7041538</v>
+        <v>7041535</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15333,6 +15332,21 @@
       <c r="AH128" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -15350,10 +15364,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130022333</v>
+        <v>130022265</v>
       </c>
       <c r="B129" t="n">
-        <v>91635</v>
+        <v>83073</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15361,30 +15375,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -15392,10 +15402,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>506291</v>
+        <v>506287</v>
       </c>
       <c r="R129" t="n">
-        <v>7041817</v>
+        <v>7041437</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15475,10 +15485,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130022336</v>
+        <v>130022300</v>
       </c>
       <c r="B130" t="n">
-        <v>91635</v>
+        <v>57741</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15486,28 +15496,29 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -15517,10 +15528,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>505807</v>
+        <v>506005</v>
       </c>
       <c r="R130" t="n">
-        <v>7041535</v>
+        <v>7041651</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15555,34 +15566,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -15718,7 +15718,7 @@
         <v>130022282</v>
       </c>
       <c r="B132" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15825,10 +15825,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130022293</v>
+        <v>130022280</v>
       </c>
       <c r="B133" t="n">
-        <v>57741</v>
+        <v>91641</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15836,29 +15836,28 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -15868,10 +15867,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>506204</v>
+        <v>505798</v>
       </c>
       <c r="R133" t="n">
-        <v>7041525</v>
+        <v>7041503</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15906,23 +15905,39 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -16055,10 +16070,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130022317</v>
+        <v>130022293</v>
       </c>
       <c r="B135" t="n">
-        <v>57900</v>
+        <v>57741</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16066,50 +16081,42 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>505940</v>
+        <v>506204</v>
       </c>
       <c r="R135" t="n">
-        <v>7041639</v>
+        <v>7041525</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16144,6 +16151,11 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -16156,11 +16168,6 @@
       <c r="AH135" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>Flerskiktad skog i många delar.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -16178,10 +16185,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130022280</v>
+        <v>130022317</v>
       </c>
       <c r="B136" t="n">
-        <v>91639</v>
+        <v>57900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16189,41 +16196,50 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>505798</v>
+        <v>505940</v>
       </c>
       <c r="R136" t="n">
-        <v>7041503</v>
+        <v>7041639</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16264,7 +16280,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -16273,24 +16288,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>Flerskiktad skog i många delar.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -16638,37 +16638,42 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130022350</v>
+        <v>130022302</v>
       </c>
       <c r="B140" t="n">
-        <v>79351</v>
+        <v>57741</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -16676,10 +16681,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>505800</v>
+        <v>506031</v>
       </c>
       <c r="R140" t="n">
-        <v>7041447</v>
+        <v>7041663</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16714,24 +16719,23 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av björk, sälg och rönn.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16749,42 +16753,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130022302</v>
+        <v>130022350</v>
       </c>
       <c r="B141" t="n">
-        <v>57741</v>
+        <v>79351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -16792,10 +16791,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>506031</v>
+        <v>505800</v>
       </c>
       <c r="R141" t="n">
-        <v>7041663</v>
+        <v>7041447</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16830,23 +16829,24 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av björk, sälg och rönn.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -16867,7 +16867,7 @@
         <v>130022277</v>
       </c>
       <c r="B142" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130022292</v>
+        <v>130022299</v>
       </c>
       <c r="B144" t="n">
         <v>57741</v>
@@ -17172,10 +17172,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>506242</v>
+        <v>506050</v>
       </c>
       <c r="R144" t="n">
-        <v>7041507</v>
+        <v>7041531</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17244,7 +17244,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130022299</v>
+        <v>130022292</v>
       </c>
       <c r="B145" t="n">
         <v>57741</v>
@@ -17287,10 +17287,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>506050</v>
+        <v>506242</v>
       </c>
       <c r="R145" t="n">
-        <v>7041531</v>
+        <v>7041507</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17583,7 +17583,7 @@
         <v>130022341</v>
       </c>
       <c r="B148" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17819,10 +17819,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130022270</v>
+        <v>130022318</v>
       </c>
       <c r="B150" t="n">
-        <v>83073</v>
+        <v>57900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17830,37 +17830,50 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>505972</v>
+        <v>505748</v>
       </c>
       <c r="R150" t="n">
-        <v>7041657</v>
+        <v>7041442</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17901,28 +17914,12 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
@@ -17940,10 +17937,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130022269</v>
+        <v>130022346</v>
       </c>
       <c r="B151" t="n">
-        <v>83073</v>
+        <v>82939</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17951,21 +17948,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17978,10 +17975,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>506062</v>
+        <v>505969</v>
       </c>
       <c r="R151" t="n">
-        <v>7041545</v>
+        <v>7041653</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18061,10 +18058,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130022344</v>
+        <v>130022337</v>
       </c>
       <c r="B152" t="n">
-        <v>82939</v>
+        <v>91655</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18072,26 +18069,30 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -18099,10 +18100,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>506043</v>
+        <v>505832</v>
       </c>
       <c r="R152" t="n">
-        <v>7041532</v>
+        <v>7041497</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18150,21 +18151,6 @@
       <c r="AH152" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -18182,10 +18168,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130022337</v>
+        <v>130022344</v>
       </c>
       <c r="B153" t="n">
-        <v>91653</v>
+        <v>82939</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18193,30 +18179,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
@@ -18224,10 +18206,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>505832</v>
+        <v>506043</v>
       </c>
       <c r="R153" t="n">
-        <v>7041497</v>
+        <v>7041532</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18275,6 +18257,21 @@
       <c r="AH153" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -18292,10 +18289,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130022346</v>
+        <v>130022269</v>
       </c>
       <c r="B154" t="n">
-        <v>82939</v>
+        <v>83073</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18303,21 +18300,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18330,10 +18327,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>505969</v>
+        <v>506062</v>
       </c>
       <c r="R154" t="n">
-        <v>7041653</v>
+        <v>7041545</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18413,10 +18410,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130022318</v>
+        <v>130022270</v>
       </c>
       <c r="B155" t="n">
-        <v>57900</v>
+        <v>83073</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18424,50 +18421,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>505748</v>
+        <v>505972</v>
       </c>
       <c r="R155" t="n">
-        <v>7041442</v>
+        <v>7041657</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18508,12 +18492,28 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>
@@ -18531,7 +18531,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130022296</v>
+        <v>130022313</v>
       </c>
       <c r="B156" t="n">
         <v>57741</v>
@@ -18574,10 +18574,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>506041</v>
+        <v>505812</v>
       </c>
       <c r="R156" t="n">
-        <v>7041525</v>
+        <v>7041551</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18646,7 +18646,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130022297</v>
+        <v>130022296</v>
       </c>
       <c r="B157" t="n">
         <v>57741</v>
@@ -18689,10 +18689,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>506062</v>
+        <v>506041</v>
       </c>
       <c r="R157" t="n">
-        <v>7041558</v>
+        <v>7041525</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18761,7 +18761,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130022313</v>
+        <v>130022297</v>
       </c>
       <c r="B158" t="n">
         <v>57741</v>
@@ -18804,10 +18804,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>505812</v>
+        <v>506062</v>
       </c>
       <c r="R158" t="n">
-        <v>7041551</v>
+        <v>7041558</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18876,37 +18876,41 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130022324</v>
+        <v>130022281</v>
       </c>
       <c r="B159" t="n">
-        <v>83071</v>
+        <v>92359</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6486</v>
+        <v>3298</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -18914,10 +18918,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>505884</v>
+        <v>506113</v>
       </c>
       <c r="R159" t="n">
-        <v>7041508</v>
+        <v>7041592</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18965,26 +18969,6 @@
       <c r="AH159" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>
@@ -19002,39 +18986,40 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130022281</v>
+        <v>130022315</v>
       </c>
       <c r="B160" t="n">
-        <v>92357</v>
+        <v>57741</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -19044,10 +19029,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>506113</v>
+        <v>505763</v>
       </c>
       <c r="R160" t="n">
-        <v>7041592</v>
+        <v>7041524</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19082,19 +19067,38 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -19227,27 +19231,27 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>130022315</v>
+        <v>130022319</v>
       </c>
       <c r="B162" t="n">
-        <v>57741</v>
+        <v>58377</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -19255,25 +19259,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>505763</v>
+        <v>505775</v>
       </c>
       <c r="R162" t="n">
-        <v>7041524</v>
+        <v>7041440</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19310,7 +19322,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Observerades i gammal grandominerad skog med inslag av björk och enstaka sälg och rönn.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19325,21 +19337,6 @@
       <c r="AH162" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr"/>
@@ -19357,10 +19354,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>130022319</v>
+        <v>130022324</v>
       </c>
       <c r="B163" t="n">
-        <v>58377</v>
+        <v>83071</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19368,50 +19365,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>102125</v>
+        <v>6486</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>505775</v>
+        <v>505884</v>
       </c>
       <c r="R163" t="n">
-        <v>7041440</v>
+        <v>7041508</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19446,23 +19430,39 @@
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Observerades i gammal grandominerad skog med inslag av björk och enstaka sälg och rönn.</t>
-        </is>
-      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -19480,10 +19480,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130022275</v>
+        <v>130022339</v>
       </c>
       <c r="B164" t="n">
-        <v>83073</v>
+        <v>91661</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19491,26 +19491,26 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -19518,10 +19518,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>505826</v>
+        <v>506254</v>
       </c>
       <c r="R164" t="n">
-        <v>7041551</v>
+        <v>7041527</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19601,10 +19601,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130022342</v>
+        <v>130022321</v>
       </c>
       <c r="B165" t="n">
-        <v>79095</v>
+        <v>91592</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19612,34 +19612,30 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
@@ -19647,10 +19643,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>506039</v>
+        <v>506094</v>
       </c>
       <c r="R165" t="n">
-        <v>7041535</v>
+        <v>7041565</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19683,11 +19679,6 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar, på gran.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19735,10 +19726,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>130022264</v>
+        <v>130022342</v>
       </c>
       <c r="B166" t="n">
-        <v>83073</v>
+        <v>79095</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19746,25 +19737,33 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
@@ -19773,10 +19772,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>506392</v>
+        <v>506039</v>
       </c>
       <c r="R166" t="n">
-        <v>7041487</v>
+        <v>7041535</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19809,6 +19808,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar, på gran.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19977,52 +19981,61 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>130022334</v>
+        <v>130022338</v>
       </c>
       <c r="B168" t="n">
-        <v>91635</v>
+        <v>57733</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1108</v>
+        <v>100110</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>506052</v>
+        <v>506398</v>
       </c>
       <c r="R168" t="n">
-        <v>7041514</v>
+        <v>7041609</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20063,28 +20076,12 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -20102,10 +20099,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>130022339</v>
+        <v>130022334</v>
       </c>
       <c r="B169" t="n">
-        <v>91659</v>
+        <v>91637</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20113,19 +20110,23 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
@@ -20140,10 +20141,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>506254</v>
+        <v>506052</v>
       </c>
       <c r="R169" t="n">
-        <v>7041527</v>
+        <v>7041514</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20223,10 +20224,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>130022321</v>
+        <v>130022275</v>
       </c>
       <c r="B170" t="n">
-        <v>91590</v>
+        <v>83073</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20234,30 +20235,26 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>112</v>
+        <v>6440</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
@@ -20265,10 +20262,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>506094</v>
+        <v>505826</v>
       </c>
       <c r="R170" t="n">
-        <v>7041565</v>
+        <v>7041551</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20348,61 +20345,48 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>130022338</v>
+        <v>130022264</v>
       </c>
       <c r="B171" t="n">
-        <v>57733</v>
+        <v>83073</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100110</v>
+        <v>6440</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Kiltermyren, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>506398</v>
+        <v>506392</v>
       </c>
       <c r="R171" t="n">
-        <v>7041609</v>
+        <v>7041487</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20443,12 +20427,28 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
